--- a/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
+++ b/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
@@ -544,11 +544,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>35</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.5987</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -582,25 +586,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1784987195</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1784988000</v>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1784987195</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -630,11 +644,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>12</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.7862</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.7862</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -668,25 +686,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1784986980</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1784988000</v>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1784986980</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -716,11 +744,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>37</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.7875</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.7875</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -754,25 +786,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1784986980</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1784988000</v>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1784986980</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -802,11 +844,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>69</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.6012</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.6012</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -840,25 +886,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1784986978</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1784988000</v>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1784986978</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -888,11 +944,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.2712</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.2712</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -926,25 +986,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1784984833</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1784988000</v>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1784984833</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -961,7 +1031,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
+          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -974,11 +1044,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.7887</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.7887</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -1012,29 +1086,39 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1784984812</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1784988000</v>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1784984812</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>10.745559</t>
+          <t>4.733718</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1047,7 +1131,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
+          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1057,14 +1141,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.5737</v>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.7887</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -1090,7 +1178,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1098,29 +1186,39 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1784984812</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1784988000</v>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1784984812</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>23.46041</t>
+          <t>10.745559</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1133,7 +1231,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
+          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1143,14 +1241,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.7887</v>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.5737</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -1176,7 +1278,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1184,29 +1286,39 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1784984812</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1784988000</v>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1784984812</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>4.733718</t>
+          <t>23.46041</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1232,11 +1344,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.2712</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.2712</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -1270,25 +1386,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1784984810</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1784988000</v>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1784984810</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1318,11 +1444,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.2712</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.2712</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -1356,25 +1486,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1784984670</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1784988000</v>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1784984670</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1404,11 +1544,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>16</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.2712</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.2712</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -1442,25 +1586,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1784984617</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1784988000</v>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1784984617</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1490,11 +1644,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>16</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.2712</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.2712</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -1528,25 +1686,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1784984581</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1784988000</v>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1784984581</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1576,11 +1744,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>16</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.2712</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.2712</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -1614,25 +1786,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1784984563</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1784988000</v>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1784984563</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1662,11 +1844,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.3013</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.3013</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -1700,25 +1886,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1784984538</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1784988000</v>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1784984538</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1748,11 +1944,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>21</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.4363</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.4363</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -1786,25 +1986,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1784984537</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1784988000</v>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1784984537</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1834,11 +2044,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>38</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.5537</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.5537</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -1872,25 +2086,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1784984536</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1784988000</v>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1784984536</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1920,11 +2144,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>29</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.5537</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.5537</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1958,25 +2186,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1784984502</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1784988000</v>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1784984502</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2006,11 +2244,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>25</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.5537</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.5537</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -2044,25 +2286,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1784984501</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1784988000</v>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1784984501</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2092,11 +2344,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.3013</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.3013</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -2130,25 +2386,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1784984431</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1784988000</v>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1784984431</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2178,11 +2444,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>27</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.4537</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.4537</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -2216,25 +2486,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1784984405</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1784988000</v>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1784984405</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2264,11 +2544,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>35</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.595</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -2302,25 +2586,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1784984404</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1784988000</v>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1784984404</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2350,11 +2644,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>22</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.7712</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.7712</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -2388,25 +2686,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1784984403</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1784988000</v>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1784984403</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2436,11 +2744,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1.775</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -2474,25 +2786,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1784984403</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1784988000</v>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1784984403</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2522,11 +2844,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>17</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.2988</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.2988</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -2560,25 +2886,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1784984402</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1784988000</v>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1784984402</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2608,11 +2944,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>41</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1.685</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.685</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -2646,25 +2986,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1784984401</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1784988000</v>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1784984401</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2694,11 +3044,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1.5537</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.5537</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -2732,25 +3086,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1784983849</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1784988000</v>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1784983849</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2780,11 +3144,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>25</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1.5513</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -2818,25 +3186,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1784983797</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1784988000</v>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1784983797</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2853,7 +3231,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
+          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2863,14 +3241,18 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1.5513</v>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.7712</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -2896,7 +3278,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2904,29 +3286,39 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1784983703</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1784988000</v>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1784983703</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4.389968</t>
+          <t>5.770489</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -2939,7 +3331,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
+          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2949,14 +3341,18 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1.7712</v>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -2982,7 +3378,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2990,29 +3386,39 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1784983703</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1784988000</v>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1784983703</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5.770489</t>
+          <t>4.389968</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3038,11 +3444,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>12</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1.5513</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -3076,25 +3486,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1784983480</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1784988000</v>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1784983480</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3124,11 +3544,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1.5513</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -3162,25 +3586,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1784983361</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1784988000</v>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1784983361</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3210,11 +3644,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1.215</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.215</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -3248,25 +3686,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1784981088</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1784988000</v>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1784981088</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3296,11 +3744,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>16</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1.7712</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.7712</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
@@ -3334,25 +3786,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1784981082</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1784988000</v>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1784981082</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3382,11 +3844,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>19</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.5513</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
@@ -3420,25 +3886,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1784980847</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1784988000</v>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1784980847</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3468,11 +3944,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>22</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1.555</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -3506,25 +3986,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1784977858</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1784988000</v>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1784977858</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3554,11 +4044,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>27</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.555</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -3592,25 +4086,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1784977853</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1784988000</v>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1784977853</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3640,11 +4144,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>20</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1.435</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.435</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -3678,25 +4186,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1784968614</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1784988000</v>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1784968614</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3726,11 +4244,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.56</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -3764,25 +4286,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1784907257</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1784988000</v>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1784907257</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3812,11 +4344,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>26</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1.5737</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.5737</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -3850,25 +4386,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1784907053</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1784988000</v>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1784907053</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3898,11 +4444,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>14</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1.315</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -3936,25 +4486,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1784907041</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1784988000</v>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3984,11 +4544,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>14</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1.315</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -4022,25 +4586,35 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1784907041</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1784988000</v>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4057,7 +4631,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4070,11 +4644,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>22</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1.4625</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
@@ -4100,7 +4678,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4108,29 +4686,39 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q43" t="n">
-        <v>1</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1784907040</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1784988000</v>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1784907040</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>47.589189</t>
+          <t>47.046509</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4143,7 +4731,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4156,11 +4744,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>26</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1.57</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
@@ -4186,7 +4778,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4194,29 +4786,39 @@
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1784907040</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1784988000</v>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1784907040</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>47.046509</t>
+          <t>47.589189</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">

--- a/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
+++ b/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
+++ b/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,30 +531,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x65bc0b70a6148d6f136b1552723c33dcf058e2ee7e6097ad6d18a39367f4821b</t>
+          <t>0x79c1f616b380c93f42fe785c942a2cc39edc55c4cdd4d5b6a09024c926a74f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>11.22999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5987</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>1.5413</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
@@ -563,32 +563,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1784987195</t>
+          <t>1785237449</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>59.090338</t>
+          <t>20.748249</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -626,35 +626,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd5e3b95bd82e0d7627a9203f0fe8fdd3b068e15fd373a543e05b207e66faf2a0</t>
+          <t>0xce612ac2221331f875649902eb6a0cde4b9db2f0f597bbc86e7caced63d25b99</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7862</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>1.4412</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
@@ -663,32 +667,32 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -708,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1784986980</t>
+          <t>1785236520</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>16.327479</t>
+          <t>26.583569</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -726,35 +730,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xbfc0a906e601c3195b374e6d33b07e4c0b0dcbf09e05e45b8bd53226678d5d88</t>
+          <t>0x7ae96391e38cfe39539922631da2025b36f57f1831d5f35ec6338463f27cb2a2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7875</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>1.5525</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
@@ -763,32 +771,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -808,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1784986980</t>
+          <t>1785236069</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>47.105879</t>
+          <t>1.864253</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -826,35 +834,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x5724a3badfc2012619fbf8e1a14ab0e7f4c66de896315371280c186505e86b85</t>
+          <t>0xc979cd389b2d4ca831b9a44b7738a2ae46abf46b1bd95d0fbe5b654a09413b1e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6012</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>1.4525</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
@@ -863,32 +875,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -908,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1784986978</t>
+          <t>1785235526</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>114.884008</t>
+          <t>12.353591</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -926,12 +938,16 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xf825a9ec3149d5a232253fd07078e2ed75a62b287df75e59fbb6c1546f6912a3</t>
+          <t>0x65bc0b70a6148d6f136b1552723c33dcf058e2ee7e6097ad6d18a39367f4821b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -946,12 +962,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -978,7 +994,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1008,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1784984833</t>
+          <t>1784987195</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1018,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>58.211982</t>
+          <t>59.090338</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1031,7 +1047,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
+          <t>0xd5e3b95bd82e0d7627a9203f0fe8fdd3b068e15fd373a543e05b207e66faf2a0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1046,12 +1062,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7887</t>
+          <t>1.7862</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1078,7 +1094,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1108,7 +1124,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1784986980</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1118,7 +1134,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4.733718</t>
+          <t>16.327479</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1131,7 +1147,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
+          <t>0xbfc0a906e601c3195b374e6d33b07e4c0b0dcbf09e05e45b8bd53226678d5d88</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1146,12 +1162,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7887</t>
+          <t>1.7875</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1178,7 +1194,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1208,7 +1224,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1784986980</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>10.745559</t>
+          <t>47.105879</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1231,12 +1247,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
+          <t>0x5724a3badfc2012619fbf8e1a14ab0e7f4c66de896315371280c186505e86b85</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1246,12 +1262,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.6012</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1308,7 +1324,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1784986978</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1318,7 +1334,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>23.46041</t>
+          <t>114.884008</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1331,7 +1347,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x6c8964e487e133d59a699205a9a6514d54217a61ad5ca3887aa005a89c8cbdfa</t>
+          <t>0xf825a9ec3149d5a232253fd07078e2ed75a62b287df75e59fbb6c1546f6912a3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1408,7 +1424,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1784984810</t>
+          <t>1784984833</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1418,7 +1434,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>58.209253</t>
+          <t>58.211982</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1431,27 +1447,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xb8b680dda4305fed43c95dc6dbc059c9678abe5f31da65b83ac57ecd5c8d3903</t>
+          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1478,7 +1494,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1508,7 +1524,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1784984670</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1518,7 +1534,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>4.733718</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1531,27 +1547,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x374cde0708e064be0b99fea4bb71434540b7ca7bbd1a444cb12a8b14c6aa3c48</t>
+          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1578,7 +1594,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1608,7 +1624,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1784984617</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1618,7 +1634,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>10.745559</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1631,12 +1647,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x4c094ddc4f89a7cbd768baf6a26f7e686ead028a4b15ee75fd8f4927e1ad7989</t>
+          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1646,12 +1662,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1678,7 +1694,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1708,7 +1724,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1784984581</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1718,7 +1734,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>23.46041</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1731,7 +1747,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x7dd8d48e4f9e00707e79d58d5900292571189d9de19bd23c6c6a9a433ea96f72</t>
+          <t>0x6c8964e487e133d59a699205a9a6514d54217a61ad5ca3887aa005a89c8cbdfa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1746,7 +1762,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1808,7 +1824,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1784984563</t>
+          <t>1784984810</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1818,7 +1834,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>58.209253</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1831,7 +1847,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x7354c940dd56ae7caca9fa9b1a548dcf53e1a3516f531216c677cf582affb4fe</t>
+          <t>0xb8b680dda4305fed43c95dc6dbc059c9678abe5f31da65b83ac57ecd5c8d3903</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1846,12 +1862,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1908,7 +1924,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1784984538</t>
+          <t>1784984670</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1918,7 +1934,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>31.184232</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1931,12 +1947,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xdc3c1508859b265a9cc7ea3dadc58bb672f939bf46cde2c06081ec2891a03946</t>
+          <t>0x374cde0708e064be0b99fea4bb71434540b7ca7bbd1a444cb12a8b14c6aa3c48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1946,12 +1962,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1978,7 +1994,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2008,7 +2024,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1784984537</t>
+          <t>1784984617</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2018,7 +2034,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48.297994</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2031,12 +2047,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x0bf6c8f6ea5d7452bf543eb72d99a66c1b6ff74a5e56b4ad9449b6870f225d2d</t>
+          <t>0x4c094ddc4f89a7cbd768baf6a26f7e686ead028a4b15ee75fd8f4927e1ad7989</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2046,12 +2062,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -2078,7 +2094,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2108,7 +2124,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1784984536</t>
+          <t>1784984581</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2118,7 +2134,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>68.833427</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2131,12 +2147,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xa4b5b4c3c3766e7d708b5373412745aa0b0d5f4c097f5451a2210d6d019269c6</t>
+          <t>0x7dd8d48e4f9e00707e79d58d5900292571189d9de19bd23c6c6a9a433ea96f72</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2146,12 +2162,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -2178,7 +2194,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2208,7 +2224,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1784984502</t>
+          <t>1784984563</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2218,7 +2234,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>53.355738</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2231,12 +2247,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xfac3960037b540d1b0b49f14ff5313d7db5bd6320c356e510ef3e6bdaca6d1ff</t>
+          <t>0x7354c940dd56ae7caca9fa9b1a548dcf53e1a3516f531216c677cf582affb4fe</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2246,12 +2262,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -2278,7 +2294,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2308,7 +2324,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1784984501</t>
+          <t>1784984538</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2318,7 +2334,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>46.408957</t>
+          <t>31.184232</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2331,12 +2347,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xf3b65016998beda20548812c7503abc20be0fa3abedc59c3ac7e08e6b82c70f1</t>
+          <t>0xdc3c1508859b265a9cc7ea3dadc58bb672f939bf46cde2c06081ec2891a03946</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2346,12 +2362,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2378,7 +2394,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2408,7 +2424,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1784984431</t>
+          <t>1784984537</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2418,7 +2434,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>22.912332</t>
+          <t>48.297994</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2431,12 +2447,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xa04fcfb1b689fd17d1c3c66ac2ed73a6e0b99d30bdfd296529ca6549b4642440</t>
+          <t>0x0bf6c8f6ea5d7452bf543eb72d99a66c1b6ff74a5e56b4ad9449b6870f225d2d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2446,12 +2462,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2478,7 +2494,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2508,7 +2524,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1784984405</t>
+          <t>1784984536</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2518,7 +2534,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>60.187328</t>
+          <t>68.833427</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2531,12 +2547,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xb07983b62c387b953f021bde51a561f510162701d56466ec78a20a598c01d8c4</t>
+          <t>0xa4b5b4c3c3766e7d708b5373412745aa0b0d5f4c097f5451a2210d6d019269c6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2546,12 +2562,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2578,7 +2594,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2608,7 +2624,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1784984404</t>
+          <t>1784984502</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2618,7 +2634,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>60.197529</t>
+          <t>53.355738</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2631,27 +2647,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xc41db21ce0b5921299bba16424467dff9a9a6eb4d744a5aadf04422f8138f34f</t>
+          <t>0xfac3960037b540d1b0b49f14ff5313d7db5bd6320c356e510ef3e6bdaca6d1ff</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2678,7 +2694,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2708,7 +2724,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1784984403</t>
+          <t>1784984501</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2718,7 +2734,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>29.185737</t>
+          <t>46.408957</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2731,27 +2747,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x97d57842a441d56ad4d0172a6e2460bdd3644bd55476d419863d144ec4fb3f02</t>
+          <t>0xf3b65016998beda20548812c7503abc20be0fa3abedc59c3ac7e08e6b82c70f1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2778,7 +2794,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2808,7 +2824,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1784984403</t>
+          <t>1784984431</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2818,7 +2834,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.444439</t>
+          <t>22.912332</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2831,7 +2847,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x54a44d2ce4be4b546daee52057d4611c0f1d29571a9747f66b3462780e888ae0</t>
+          <t>0xa04fcfb1b689fd17d1c3c66ac2ed73a6e0b99d30bdfd296529ca6549b4642440</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2846,12 +2862,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2988</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2878,7 +2894,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2908,7 +2924,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1784984402</t>
+          <t>1784984405</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2918,7 +2934,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>60.178243</t>
+          <t>60.187328</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2931,7 +2947,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xf9d293335e6b1b3fd21eba9ec71cbbd6cbce398d5d606b38175d3776a077cb91</t>
+          <t>0xb07983b62c387b953f021bde51a561f510162701d56466ec78a20a598c01d8c4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2946,12 +2962,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2978,7 +2994,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xaf0827308b557ecc964e4c608c6b71f345660fa965da2a0e02882ee62ce45e49</t>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,7 +3024,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1784984401</t>
+          <t>1784984404</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3018,7 +3034,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>60.189781</t>
+          <t>60.197529</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3031,27 +3047,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x80f610f55e907d511b2c5a8d77d03f9aca143e4e50b6d7fba92997ba46481bde</t>
+          <t>0xc41db21ce0b5921299bba16424467dff9a9a6eb4d744a5aadf04422f8138f34f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.7712</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -3078,7 +3094,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3108,7 +3124,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1784983849</t>
+          <t>1784984403</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3118,7 +3134,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>11.988786</t>
+          <t>29.185737</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3131,7 +3147,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x6e3d6f822ebfe70f563004b4a5a4a6303f1d1cb9677e6e3a56324cda8cc92ba7</t>
+          <t>0x97d57842a441d56ad4d0172a6e2460bdd3644bd55476d419863d144ec4fb3f02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3141,17 +3157,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -3178,7 +3194,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3208,7 +3224,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1784983797</t>
+          <t>1784984403</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3218,7 +3234,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>46.150404</t>
+          <t>4.444439</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3231,27 +3247,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
+          <t>0x54a44d2ce4be4b546daee52057d4611c0f1d29571a9747f66b3462780e888ae0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.2988</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -3278,7 +3294,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3308,7 +3324,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1784983703</t>
+          <t>1784984402</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3318,7 +3334,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>5.770489</t>
+          <t>60.178243</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3331,12 +3347,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
+          <t>0xf9d293335e6b1b3fd21eba9ec71cbbd6cbce398d5d606b38175d3776a077cb91</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3346,12 +3362,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -3378,7 +3394,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0xaf0827308b557ecc964e4c608c6b71f345660fa965da2a0e02882ee62ce45e49</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3408,7 +3424,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1784983703</t>
+          <t>1784984401</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3418,7 +3434,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>4.389968</t>
+          <t>60.189781</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3431,12 +3447,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x589562dc55239bfc299045a0e5bbfed420cc8f286ee7326d34ed350f83ecdd45</t>
+          <t>0x80f610f55e907d511b2c5a8d77d03f9aca143e4e50b6d7fba92997ba46481bde</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3446,12 +3462,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -3508,7 +3524,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1784983480</t>
+          <t>1784983849</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3518,7 +3534,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>22.284118</t>
+          <t>11.988786</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3531,7 +3547,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x629a7bab69ed2f6eae5804065863061a8e5f95bfbf35104c3a1d130585e021ca</t>
+          <t>0x6e3d6f822ebfe70f563004b4a5a4a6303f1d1cb9677e6e3a56324cda8cc92ba7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3546,7 +3562,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3608,7 +3624,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1784983361</t>
+          <t>1784983797</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3618,7 +3634,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.228408</t>
+          <t>46.150404</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3631,27 +3647,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x888b7311174b291a1eeccf40a054d1599070da16bd2f2f7adea95d18002cc686</t>
+          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xB1854fc8aD8ce649EA80D007Fc67d318a239a5DA</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.7712</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -3708,7 +3724,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1784981088</t>
+          <t>1784983703</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3718,7 +3734,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1.443442</t>
+          <t>5.770489</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3731,7 +3747,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x5d44678e836886d72dc3bddfca4b44d2be2bfa7f56096dbedd259cac92e30df3</t>
+          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3741,17 +3757,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -3778,7 +3794,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3808,7 +3824,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1784981082</t>
+          <t>1784983703</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3818,7 +3834,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>21.377037</t>
+          <t>4.389968</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3831,7 +3847,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x5a96bb0ca1d506186a0e2c1c2e13d657784bbb03ad3f75e66db86da80f485bae</t>
+          <t>0x589562dc55239bfc299045a0e5bbfed420cc8f286ee7326d34ed350f83ecdd45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3846,7 +3862,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3908,7 +3924,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1784980847</t>
+          <t>1784983480</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -3918,7 +3934,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>35.743728</t>
+          <t>22.284118</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -3931,12 +3947,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xe6e61e0b4573e8e2199880691f7803f1943269d2b2b955ea7282a833c4dbc3c6</t>
+          <t>0x629a7bab69ed2f6eae5804065863061a8e5f95bfbf35104c3a1d130585e021ca</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3946,12 +3962,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -4008,7 +4024,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1784977858</t>
+          <t>1784983361</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4018,7 +4034,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>39.775279</t>
+          <t>2.228408</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4031,12 +4047,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x668fc309ba15ebe234fe9dd2d2bf696a9f4000c9ac85f8e7d55c998a052968dc</t>
+          <t>0x888b7311174b291a1eeccf40a054d1599070da16bd2f2f7adea95d18002cc686</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0xB1854fc8aD8ce649EA80D007Fc67d318a239a5DA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4046,12 +4062,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -4078,7 +4094,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4108,7 +4124,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1784977853</t>
+          <t>1784981088</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4118,7 +4134,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>49.797748</t>
+          <t>1.443442</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4131,12 +4147,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xabcdef492212262464335967adbaa23c5214ede2fab0ea2a12bce6e0027067aa</t>
+          <t>0x5d44678e836886d72dc3bddfca4b44d2be2bfa7f56096dbedd259cac92e30df3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4146,12 +4162,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.7712</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -4178,7 +4194,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4208,7 +4224,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1784968614</t>
+          <t>1784981082</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4218,7 +4234,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>47.149425</t>
+          <t>21.377037</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4231,12 +4247,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xf7e34584abe1fc7da16770ad9dc2fe59e91a45480c1ff509d55070c7d811c7e2</t>
+          <t>0x5a96bb0ca1d506186a0e2c1c2e13d657784bbb03ad3f75e66db86da80f485bae</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x516bfc7CE57c0E1734388ECed5Bb9454aA6aeFae</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4246,12 +4262,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -4278,7 +4294,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4308,7 +4324,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1784907257</t>
+          <t>1784980847</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4318,7 +4334,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>17.857143</t>
+          <t>35.743728</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4331,12 +4347,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x030841d8eff7e23d98d8319e71f99f9eb17cb2a743343cfac134410b86f1178e</t>
+          <t>0xe6e61e0b4573e8e2199880691f7803f1943269d2b2b955ea7282a833c4dbc3c6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4346,12 +4362,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -4378,7 +4394,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4408,7 +4424,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1784907053</t>
+          <t>1784977858</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4418,7 +4434,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>46.28739</t>
+          <t>39.775279</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4431,12 +4447,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xd486facb98ea7c7e7b67efb74b5231332788279dbd71dce40eea54aecf5d870e</t>
+          <t>0x668fc309ba15ebe234fe9dd2d2bf696a9f4000c9ac85f8e7d55c998a052968dc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4446,12 +4462,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -4478,7 +4494,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4508,7 +4524,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1784907041</t>
+          <t>1784977853</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4518,7 +4534,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>47.587302</t>
+          <t>49.797748</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4531,7 +4547,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x8a9596cb004924470885fe466db8f8d059fcb9d1b24e71490dd35bfeba65a98d</t>
+          <t>0xabcdef492212262464335967adbaa23c5214ede2fab0ea2a12bce6e0027067aa</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4541,17 +4557,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -4578,7 +4594,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4608,7 +4624,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1784907041</t>
+          <t>1784968614</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4618,7 +4634,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>47.555556</t>
+          <t>47.149425</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4631,12 +4647,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+          <t>0xf7e34584abe1fc7da16770ad9dc2fe59e91a45480c1ff509d55070c7d811c7e2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x516bfc7CE57c0E1734388ECed5Bb9454aA6aeFae</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4646,12 +4662,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -4708,7 +4724,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1784907040</t>
+          <t>1784907257</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4718,7 +4734,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>47.046509</t>
+          <t>17.857143</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4731,7 +4747,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+          <t>0x030841d8eff7e23d98d8319e71f99f9eb17cb2a743343cfac134410b86f1178e</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4746,12 +4762,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -4778,55 +4794,455 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1784907053</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>46.28739</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0xd486facb98ea7c7e7b67efb74b5231332788279dbd71dce40eea54aecf5d870e</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>47.587302</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x8a9596cb004924470885fe466db8f8d059fcb9d1b24e71490dd35bfeba65a98d</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>47.555556</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1784907040</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>47.046509</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>1784907040</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>1784988000</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>47.589189</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
+++ b/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V48"/>
+  <dimension ref="A1:V52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x79c1f616b380c93f42fe785c942a2cc39edc55c4cdd4d5b6a09024c926a74f60</t>
+          <t>0xda116ce959332ba41194293702cd84c233a1aa5dc72f06cf3a812e3b16c89f50</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.22999</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785237449</t>
+          <t>1785267812</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20.748249</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xce612ac2221331f875649902eb6a0cde4b9db2f0f597bbc86e7caced63d25b99</t>
+          <t>0xf8236e3ab62a3112d2d962ecd3674bb25592395a1e4e2b076102954ddd699eb7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -667,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785236520</t>
+          <t>1785267777</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>26.583569</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x7ae96391e38cfe39539922631da2025b36f57f1831d5f35ec6338463f27cb2a2</t>
+          <t>0x9c098bbf30f27adf5fb61d9dc7cffe685f61dacbc06ffd60f2ab0ab57bf9a296</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -771,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785236069</t>
+          <t>1785267742</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.864253</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xc979cd389b2d4ca831b9a44b7738a2ae46abf46b1bd95d0fbe5b654a09413b1e</t>
+          <t>0x4c622a3a303c2e364803ca8b5f2417b149396b0a5a454b59e42697e254ae9315</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -875,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785235526</t>
+          <t>1785267709</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>12.353591</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,30 +979,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x65bc0b70a6148d6f136b1552723c33dcf058e2ee7e6097ad6d18a39367f4821b</t>
+          <t>0x79c1f616b380c93f42fe785c942a2cc39edc55c4cdd4d5b6a09024c926a74f60</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>11.22999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5987</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>1.5413</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
@@ -979,32 +1011,32 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1024,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1784987195</t>
+          <t>1785237449</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>59.090338</t>
+          <t>20.748249</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1042,35 +1074,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xd5e3b95bd82e0d7627a9203f0fe8fdd3b068e15fd373a543e05b207e66faf2a0</t>
+          <t>0xce612ac2221331f875649902eb6a0cde4b9db2f0f597bbc86e7caced63d25b99</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7862</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>1.4412</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
@@ -1079,32 +1115,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1124,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1784986980</t>
+          <t>1785236520</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>16.327479</t>
+          <t>26.583569</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1142,35 +1178,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xbfc0a906e601c3195b374e6d33b07e4c0b0dcbf09e05e45b8bd53226678d5d88</t>
+          <t>0x7ae96391e38cfe39539922631da2025b36f57f1831d5f35ec6338463f27cb2a2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7875</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>1.5525</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
@@ -1179,32 +1219,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1224,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1784986980</t>
+          <t>1785236069</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>47.105879</t>
+          <t>1.864253</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1242,35 +1282,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x5724a3badfc2012619fbf8e1a14ab0e7f4c66de896315371280c186505e86b85</t>
+          <t>0xc979cd389b2d4ca831b9a44b7738a2ae46abf46b1bd95d0fbe5b654a09413b1e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.6012</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>1.4525</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
@@ -1279,32 +1323,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1324,17 +1368,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1784986978</t>
+          <t>1785235526</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>114.884008</t>
+          <t>12.353591</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1342,12 +1386,16 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xf825a9ec3149d5a232253fd07078e2ed75a62b287df75e59fbb6c1546f6912a3</t>
+          <t>0x65bc0b70a6148d6f136b1552723c33dcf058e2ee7e6097ad6d18a39367f4821b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1362,12 +1410,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1394,7 +1442,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1424,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1784984833</t>
+          <t>1784987195</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1434,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>58.211982</t>
+          <t>59.090338</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1447,7 +1495,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
+          <t>0xd5e3b95bd82e0d7627a9203f0fe8fdd3b068e15fd373a543e05b207e66faf2a0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1462,12 +1510,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7887</t>
+          <t>1.7862</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1494,7 +1542,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1524,7 +1572,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1784986980</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1534,7 +1582,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>4.733718</t>
+          <t>16.327479</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1547,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
+          <t>0xbfc0a906e601c3195b374e6d33b07e4c0b0dcbf09e05e45b8bd53226678d5d88</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1562,12 +1610,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7887</t>
+          <t>1.7875</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1594,7 +1642,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1624,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1784986980</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1634,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>10.745559</t>
+          <t>47.105879</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1647,12 +1695,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
+          <t>0x5724a3badfc2012619fbf8e1a14ab0e7f4c66de896315371280c186505e86b85</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1662,12 +1710,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.6012</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1724,7 +1772,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1784986978</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1734,7 +1782,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>23.46041</t>
+          <t>114.884008</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1747,7 +1795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x6c8964e487e133d59a699205a9a6514d54217a61ad5ca3887aa005a89c8cbdfa</t>
+          <t>0xf825a9ec3149d5a232253fd07078e2ed75a62b287df75e59fbb6c1546f6912a3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1824,7 +1872,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1784984810</t>
+          <t>1784984833</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1834,7 +1882,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>58.209253</t>
+          <t>58.211982</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1847,27 +1895,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xb8b680dda4305fed43c95dc6dbc059c9678abe5f31da65b83ac57ecd5c8d3903</t>
+          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1894,7 +1942,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1924,7 +1972,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1784984670</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1934,7 +1982,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>4.733718</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1947,27 +1995,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x374cde0708e064be0b99fea4bb71434540b7ca7bbd1a444cb12a8b14c6aa3c48</t>
+          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1994,7 +2042,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2024,7 +2072,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1784984617</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2034,7 +2082,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>10.745559</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2047,12 +2095,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x4c094ddc4f89a7cbd768baf6a26f7e686ead028a4b15ee75fd8f4927e1ad7989</t>
+          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2062,12 +2110,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -2094,7 +2142,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2124,7 +2172,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1784984581</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2134,7 +2182,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>23.46041</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2147,7 +2195,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x7dd8d48e4f9e00707e79d58d5900292571189d9de19bd23c6c6a9a433ea96f72</t>
+          <t>0x6c8964e487e133d59a699205a9a6514d54217a61ad5ca3887aa005a89c8cbdfa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2162,7 +2210,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2224,7 +2272,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1784984563</t>
+          <t>1784984810</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2234,7 +2282,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>58.209253</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2247,7 +2295,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x7354c940dd56ae7caca9fa9b1a548dcf53e1a3516f531216c677cf582affb4fe</t>
+          <t>0xb8b680dda4305fed43c95dc6dbc059c9678abe5f31da65b83ac57ecd5c8d3903</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2262,12 +2310,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -2324,7 +2372,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1784984538</t>
+          <t>1784984670</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2334,7 +2382,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>31.184232</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2347,12 +2395,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xdc3c1508859b265a9cc7ea3dadc58bb672f939bf46cde2c06081ec2891a03946</t>
+          <t>0x374cde0708e064be0b99fea4bb71434540b7ca7bbd1a444cb12a8b14c6aa3c48</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2362,12 +2410,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2394,7 +2442,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2424,7 +2472,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1784984537</t>
+          <t>1784984617</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2434,7 +2482,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.297994</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2447,12 +2495,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x0bf6c8f6ea5d7452bf543eb72d99a66c1b6ff74a5e56b4ad9449b6870f225d2d</t>
+          <t>0x4c094ddc4f89a7cbd768baf6a26f7e686ead028a4b15ee75fd8f4927e1ad7989</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2462,12 +2510,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2494,7 +2542,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2524,7 +2572,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1784984536</t>
+          <t>1784984581</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2534,7 +2582,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>68.833427</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2547,12 +2595,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xa4b5b4c3c3766e7d708b5373412745aa0b0d5f4c097f5451a2210d6d019269c6</t>
+          <t>0x7dd8d48e4f9e00707e79d58d5900292571189d9de19bd23c6c6a9a433ea96f72</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2562,12 +2610,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2594,7 +2642,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2624,7 +2672,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1784984502</t>
+          <t>1784984563</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2634,7 +2682,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>53.355738</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2647,12 +2695,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xfac3960037b540d1b0b49f14ff5313d7db5bd6320c356e510ef3e6bdaca6d1ff</t>
+          <t>0x7354c940dd56ae7caca9fa9b1a548dcf53e1a3516f531216c677cf582affb4fe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2662,12 +2710,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2694,7 +2742,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2724,7 +2772,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1784984501</t>
+          <t>1784984538</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2734,7 +2782,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>46.408957</t>
+          <t>31.184232</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2747,12 +2795,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xf3b65016998beda20548812c7503abc20be0fa3abedc59c3ac7e08e6b82c70f1</t>
+          <t>0xdc3c1508859b265a9cc7ea3dadc58bb672f939bf46cde2c06081ec2891a03946</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2762,12 +2810,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2794,7 +2842,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2824,7 +2872,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1784984431</t>
+          <t>1784984537</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2834,7 +2882,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>22.912332</t>
+          <t>48.297994</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2847,12 +2895,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xa04fcfb1b689fd17d1c3c66ac2ed73a6e0b99d30bdfd296529ca6549b4642440</t>
+          <t>0x0bf6c8f6ea5d7452bf543eb72d99a66c1b6ff74a5e56b4ad9449b6870f225d2d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2862,12 +2910,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2894,7 +2942,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2924,7 +2972,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1784984405</t>
+          <t>1784984536</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2934,7 +2982,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>60.187328</t>
+          <t>68.833427</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2947,12 +2995,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xb07983b62c387b953f021bde51a561f510162701d56466ec78a20a598c01d8c4</t>
+          <t>0xa4b5b4c3c3766e7d708b5373412745aa0b0d5f4c097f5451a2210d6d019269c6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2962,12 +3010,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2994,7 +3042,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3024,7 +3072,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1784984404</t>
+          <t>1784984502</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3034,7 +3082,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>60.197529</t>
+          <t>53.355738</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3047,27 +3095,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xc41db21ce0b5921299bba16424467dff9a9a6eb4d744a5aadf04422f8138f34f</t>
+          <t>0xfac3960037b540d1b0b49f14ff5313d7db5bd6320c356e510ef3e6bdaca6d1ff</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -3094,7 +3142,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3124,7 +3172,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1784984403</t>
+          <t>1784984501</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3134,7 +3182,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>29.185737</t>
+          <t>46.408957</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3147,27 +3195,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x97d57842a441d56ad4d0172a6e2460bdd3644bd55476d419863d144ec4fb3f02</t>
+          <t>0xf3b65016998beda20548812c7503abc20be0fa3abedc59c3ac7e08e6b82c70f1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -3194,7 +3242,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3224,7 +3272,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1784984403</t>
+          <t>1784984431</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3234,7 +3282,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>4.444439</t>
+          <t>22.912332</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3247,7 +3295,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x54a44d2ce4be4b546daee52057d4611c0f1d29571a9747f66b3462780e888ae0</t>
+          <t>0xa04fcfb1b689fd17d1c3c66ac2ed73a6e0b99d30bdfd296529ca6549b4642440</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3262,12 +3310,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2988</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -3294,7 +3342,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3324,7 +3372,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1784984402</t>
+          <t>1784984405</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3334,7 +3382,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>60.178243</t>
+          <t>60.187328</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3347,7 +3395,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xf9d293335e6b1b3fd21eba9ec71cbbd6cbce398d5d606b38175d3776a077cb91</t>
+          <t>0xb07983b62c387b953f021bde51a561f510162701d56466ec78a20a598c01d8c4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3362,12 +3410,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -3394,7 +3442,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xaf0827308b557ecc964e4c608c6b71f345660fa965da2a0e02882ee62ce45e49</t>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3424,7 +3472,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1784984401</t>
+          <t>1784984404</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3434,7 +3482,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>60.189781</t>
+          <t>60.197529</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3447,27 +3495,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x80f610f55e907d511b2c5a8d77d03f9aca143e4e50b6d7fba92997ba46481bde</t>
+          <t>0xc41db21ce0b5921299bba16424467dff9a9a6eb4d744a5aadf04422f8138f34f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.7712</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -3494,7 +3542,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3524,7 +3572,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1784983849</t>
+          <t>1784984403</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3534,7 +3582,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>11.988786</t>
+          <t>29.185737</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3547,7 +3595,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x6e3d6f822ebfe70f563004b4a5a4a6303f1d1cb9677e6e3a56324cda8cc92ba7</t>
+          <t>0x97d57842a441d56ad4d0172a6e2460bdd3644bd55476d419863d144ec4fb3f02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3557,17 +3605,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -3594,7 +3642,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3624,7 +3672,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1784983797</t>
+          <t>1784984403</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3634,7 +3682,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>46.150404</t>
+          <t>4.444439</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3647,27 +3695,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
+          <t>0x54a44d2ce4be4b546daee52057d4611c0f1d29571a9747f66b3462780e888ae0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.2988</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -3694,7 +3742,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3724,7 +3772,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1784983703</t>
+          <t>1784984402</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3734,7 +3782,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>5.770489</t>
+          <t>60.178243</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3747,12 +3795,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
+          <t>0xf9d293335e6b1b3fd21eba9ec71cbbd6cbce398d5d606b38175d3776a077cb91</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3762,12 +3810,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -3794,7 +3842,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0xaf0827308b557ecc964e4c608c6b71f345660fa965da2a0e02882ee62ce45e49</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3824,7 +3872,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1784983703</t>
+          <t>1784984401</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3834,7 +3882,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>4.389968</t>
+          <t>60.189781</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3847,12 +3895,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x589562dc55239bfc299045a0e5bbfed420cc8f286ee7326d34ed350f83ecdd45</t>
+          <t>0x80f610f55e907d511b2c5a8d77d03f9aca143e4e50b6d7fba92997ba46481bde</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3862,12 +3910,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -3924,7 +3972,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1784983480</t>
+          <t>1784983849</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -3934,7 +3982,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>22.284118</t>
+          <t>11.988786</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -3947,7 +3995,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x629a7bab69ed2f6eae5804065863061a8e5f95bfbf35104c3a1d130585e021ca</t>
+          <t>0x6e3d6f822ebfe70f563004b4a5a4a6303f1d1cb9677e6e3a56324cda8cc92ba7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,7 +4010,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4024,7 +4072,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1784983361</t>
+          <t>1784983797</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4034,7 +4082,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2.228408</t>
+          <t>46.150404</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4047,27 +4095,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x888b7311174b291a1eeccf40a054d1599070da16bd2f2f7adea95d18002cc686</t>
+          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xB1854fc8aD8ce649EA80D007Fc67d318a239a5DA</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.7712</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -4124,7 +4172,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1784981088</t>
+          <t>1784983703</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4134,7 +4182,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.443442</t>
+          <t>5.770489</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4147,7 +4195,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x5d44678e836886d72dc3bddfca4b44d2be2bfa7f56096dbedd259cac92e30df3</t>
+          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4157,17 +4205,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -4194,7 +4242,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4224,7 +4272,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1784981082</t>
+          <t>1784983703</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4234,7 +4282,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>21.377037</t>
+          <t>4.389968</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4247,7 +4295,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x5a96bb0ca1d506186a0e2c1c2e13d657784bbb03ad3f75e66db86da80f485bae</t>
+          <t>0x589562dc55239bfc299045a0e5bbfed420cc8f286ee7326d34ed350f83ecdd45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4262,7 +4310,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4324,7 +4372,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1784980847</t>
+          <t>1784983480</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4334,7 +4382,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>35.743728</t>
+          <t>22.284118</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4347,12 +4395,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xe6e61e0b4573e8e2199880691f7803f1943269d2b2b955ea7282a833c4dbc3c6</t>
+          <t>0x629a7bab69ed2f6eae5804065863061a8e5f95bfbf35104c3a1d130585e021ca</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4362,12 +4410,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -4424,7 +4472,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1784977858</t>
+          <t>1784983361</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4434,7 +4482,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>39.775279</t>
+          <t>2.228408</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4447,12 +4495,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x668fc309ba15ebe234fe9dd2d2bf696a9f4000c9ac85f8e7d55c998a052968dc</t>
+          <t>0x888b7311174b291a1eeccf40a054d1599070da16bd2f2f7adea95d18002cc686</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0xB1854fc8aD8ce649EA80D007Fc67d318a239a5DA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4462,12 +4510,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -4494,7 +4542,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4524,7 +4572,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1784977853</t>
+          <t>1784981088</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4534,7 +4582,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>49.797748</t>
+          <t>1.443442</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4547,12 +4595,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xabcdef492212262464335967adbaa23c5214ede2fab0ea2a12bce6e0027067aa</t>
+          <t>0x5d44678e836886d72dc3bddfca4b44d2be2bfa7f56096dbedd259cac92e30df3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4562,12 +4610,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.7712</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -4594,7 +4642,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4624,7 +4672,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1784968614</t>
+          <t>1784981082</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4634,7 +4682,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>47.149425</t>
+          <t>21.377037</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4647,12 +4695,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xf7e34584abe1fc7da16770ad9dc2fe59e91a45480c1ff509d55070c7d811c7e2</t>
+          <t>0x5a96bb0ca1d506186a0e2c1c2e13d657784bbb03ad3f75e66db86da80f485bae</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x516bfc7CE57c0E1734388ECed5Bb9454aA6aeFae</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4662,12 +4710,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -4694,7 +4742,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4724,7 +4772,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1784907257</t>
+          <t>1784980847</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4734,7 +4782,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>17.857143</t>
+          <t>35.743728</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4747,12 +4795,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x030841d8eff7e23d98d8319e71f99f9eb17cb2a743343cfac134410b86f1178e</t>
+          <t>0xe6e61e0b4573e8e2199880691f7803f1943269d2b2b955ea7282a833c4dbc3c6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4762,12 +4810,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -4794,7 +4842,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4824,7 +4872,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1784907053</t>
+          <t>1784977858</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -4834,7 +4882,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>46.28739</t>
+          <t>39.775279</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -4847,12 +4895,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xd486facb98ea7c7e7b67efb74b5231332788279dbd71dce40eea54aecf5d870e</t>
+          <t>0x668fc309ba15ebe234fe9dd2d2bf696a9f4000c9ac85f8e7d55c998a052968dc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4862,12 +4910,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -4894,7 +4942,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4924,7 +4972,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1784907041</t>
+          <t>1784977853</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -4934,7 +4982,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>47.587302</t>
+          <t>49.797748</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -4947,7 +4995,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x8a9596cb004924470885fe466db8f8d059fcb9d1b24e71490dd35bfeba65a98d</t>
+          <t>0xabcdef492212262464335967adbaa23c5214ede2fab0ea2a12bce6e0027067aa</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4957,17 +5005,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -4994,7 +5042,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5024,7 +5072,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1784907041</t>
+          <t>1784968614</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5034,7 +5082,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>47.555556</t>
+          <t>47.149425</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5047,12 +5095,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+          <t>0xf7e34584abe1fc7da16770ad9dc2fe59e91a45480c1ff509d55070c7d811c7e2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x516bfc7CE57c0E1734388ECed5Bb9454aA6aeFae</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5062,12 +5110,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -5124,7 +5172,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1784907040</t>
+          <t>1784907257</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5134,7 +5182,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>47.046509</t>
+          <t>17.857143</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5147,7 +5195,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+          <t>0x030841d8eff7e23d98d8319e71f99f9eb17cb2a743343cfac134410b86f1178e</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5162,12 +5210,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -5194,55 +5242,455 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1784907053</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>46.28739</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0xd486facb98ea7c7e7b67efb74b5231332788279dbd71dce40eea54aecf5d870e</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>47.587302</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x8a9596cb004924470885fe466db8f8d059fcb9d1b24e71490dd35bfeba65a98d</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>47.555556</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1784907040</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>47.046509</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
         <is>
           <t>1784907040</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>1784988000</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>47.589189</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
+++ b/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xda116ce959332ba41194293702cd84c233a1aa5dc72f06cf3a812e3b16c89f50</t>
+          <t>0xa9c4c39c3003eff066c3a4586da774f5987355742d4863d64aa5984bf9a94e7e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.3375</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785267812</t>
+          <t>1785298455</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.850123</t>
+          <t>2.962963</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf8236e3ab62a3112d2d962ecd3674bb25592395a1e4e2b076102954ddd699eb7</t>
+          <t>0xee5e46dfcd55125e8c178c7b7ec5808cbc3059b6cb7c8b8db7ac3eed5d7918bc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.00209</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.3375</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785267777</t>
+          <t>1785298146</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.850123</t>
+          <t>0.006193</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9c098bbf30f27adf5fb61d9dc7cffe685f61dacbc06ffd60f2ab0ab57bf9a296</t>
+          <t>0xda116ce959332ba41194293702cd84c233a1aa5dc72f06cf3a812e3b16c89f50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785267742</t>
+          <t>1785267812</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x4c622a3a303c2e364803ca8b5f2417b149396b0a5a454b59e42697e254ae9315</t>
+          <t>0xf8236e3ab62a3112d2d962ecd3674bb25592395a1e4e2b076102954ddd699eb7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785267709</t>
+          <t>1785267777</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -979,31 +979,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x79c1f616b380c93f42fe785c942a2cc39edc55c4cdd4d5b6a09024c926a74f60</t>
+          <t>0x9c098bbf30f27adf5fb61d9dc7cffe685f61dacbc06ffd60f2ab0ab57bf9a296</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.22999</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1011,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1064,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785237449</t>
+          <t>1785267742</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20.748249</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,31 +1091,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xce612ac2221331f875649902eb6a0cde4b9db2f0f597bbc86e7caced63d25b99</t>
+          <t>0x4c622a3a303c2e364803ca8b5f2417b149396b0a5a454b59e42697e254ae9315</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1115,27 +1131,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1176,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785236520</t>
+          <t>1785267709</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>26.583569</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,23 +1203,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x7ae96391e38cfe39539922631da2025b36f57f1831d5f35ec6338463f27cb2a2</t>
+          <t>0x79c1f616b380c93f42fe785c942a2cc39edc55c4cdd4d5b6a09024c926a74f60</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>11.22999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1264,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785236069</t>
+          <t>1785237449</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.864253</t>
+          <t>20.748249</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xc979cd389b2d4ca831b9a44b7738a2ae46abf46b1bd95d0fbe5b654a09413b1e</t>
+          <t>0xce612ac2221331f875649902eb6a0cde4b9db2f0f597bbc86e7caced63d25b99</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1302,12 +1318,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1368,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785235526</t>
+          <t>1785236520</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>12.353591</t>
+          <t>26.583569</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,30 +1411,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x65bc0b70a6148d6f136b1552723c33dcf058e2ee7e6097ad6d18a39367f4821b</t>
+          <t>0x7ae96391e38cfe39539922631da2025b36f57f1831d5f35ec6338463f27cb2a2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5987</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>1.5525</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
@@ -1427,32 +1443,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1472,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1784987195</t>
+          <t>1785236069</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>59.090338</t>
+          <t>1.864253</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1490,35 +1506,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd5e3b95bd82e0d7627a9203f0fe8fdd3b068e15fd373a543e05b207e66faf2a0</t>
+          <t>0xc979cd389b2d4ca831b9a44b7738a2ae46abf46b1bd95d0fbe5b654a09413b1e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7862</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>1.4525</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
@@ -1527,32 +1547,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1572,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1784986980</t>
+          <t>1785235526</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>16.327479</t>
+          <t>12.353591</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1590,32 +1610,36 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xbfc0a906e601c3195b374e6d33b07e4c0b0dcbf09e05e45b8bd53226678d5d88</t>
+          <t>0x65bc0b70a6148d6f136b1552723c33dcf058e2ee7e6097ad6d18a39367f4821b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7875</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1642,7 +1666,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1672,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1784986980</t>
+          <t>1784987195</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1682,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>47.105879</t>
+          <t>59.090338</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1695,27 +1719,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x5724a3badfc2012619fbf8e1a14ab0e7f4c66de896315371280c186505e86b85</t>
+          <t>0xd5e3b95bd82e0d7627a9203f0fe8fdd3b068e15fd373a543e05b207e66faf2a0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6012</t>
+          <t>1.7862</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1742,7 +1766,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1772,7 +1796,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1784986978</t>
+          <t>1784986980</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1782,7 +1806,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>114.884008</t>
+          <t>16.327479</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,27 +1819,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xf825a9ec3149d5a232253fd07078e2ed75a62b287df75e59fbb6c1546f6912a3</t>
+          <t>0xbfc0a906e601c3195b374e6d33b07e4c0b0dcbf09e05e45b8bd53226678d5d88</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.7875</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1842,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1872,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1784984833</t>
+          <t>1784986980</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1882,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>58.211982</t>
+          <t>47.105879</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1895,27 +1919,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
+          <t>0x5724a3badfc2012619fbf8e1a14ab0e7f4c66de896315371280c186505e86b85</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.7887</t>
+          <t>1.6012</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1942,7 +1966,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1972,7 +1996,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1784986978</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1982,7 +2006,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4.733718</t>
+          <t>114.884008</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1995,27 +2019,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
+          <t>0xf825a9ec3149d5a232253fd07078e2ed75a62b287df75e59fbb6c1546f6912a3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.7887</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -2042,7 +2066,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2072,7 +2096,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1784984833</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2082,7 +2106,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>10.745559</t>
+          <t>58.211982</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2095,7 +2119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
+          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2105,17 +2129,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -2142,7 +2166,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2182,7 +2206,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>23.46041</t>
+          <t>4.733718</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2195,27 +2219,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x6c8964e487e133d59a699205a9a6514d54217a61ad5ca3887aa005a89c8cbdfa</t>
+          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -2242,7 +2266,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2272,7 +2296,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1784984810</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2282,7 +2306,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>58.209253</t>
+          <t>10.745559</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2295,12 +2319,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xb8b680dda4305fed43c95dc6dbc059c9678abe5f31da65b83ac57ecd5c8d3903</t>
+          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2310,12 +2334,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -2342,7 +2366,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2372,7 +2396,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1784984670</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2382,7 +2406,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>23.46041</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2395,7 +2419,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x374cde0708e064be0b99fea4bb71434540b7ca7bbd1a444cb12a8b14c6aa3c48</t>
+          <t>0x6c8964e487e133d59a699205a9a6514d54217a61ad5ca3887aa005a89c8cbdfa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2410,7 +2434,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2472,7 +2496,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1784984617</t>
+          <t>1784984810</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2482,7 +2506,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>58.209253</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2495,7 +2519,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x4c094ddc4f89a7cbd768baf6a26f7e686ead028a4b15ee75fd8f4927e1ad7989</t>
+          <t>0xb8b680dda4305fed43c95dc6dbc059c9678abe5f31da65b83ac57ecd5c8d3903</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2572,7 +2596,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1784984581</t>
+          <t>1784984670</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2595,7 +2619,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x7dd8d48e4f9e00707e79d58d5900292571189d9de19bd23c6c6a9a433ea96f72</t>
+          <t>0x374cde0708e064be0b99fea4bb71434540b7ca7bbd1a444cb12a8b14c6aa3c48</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2672,7 +2696,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1784984563</t>
+          <t>1784984617</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2695,7 +2719,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x7354c940dd56ae7caca9fa9b1a548dcf53e1a3516f531216c677cf582affb4fe</t>
+          <t>0x4c094ddc4f89a7cbd768baf6a26f7e686ead028a4b15ee75fd8f4927e1ad7989</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2710,12 +2734,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2772,7 +2796,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1784984538</t>
+          <t>1784984581</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2782,7 +2806,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>31.184232</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2795,12 +2819,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xdc3c1508859b265a9cc7ea3dadc58bb672f939bf46cde2c06081ec2891a03946</t>
+          <t>0x7dd8d48e4f9e00707e79d58d5900292571189d9de19bd23c6c6a9a433ea96f72</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2810,12 +2834,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2842,7 +2866,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2872,7 +2896,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1784984537</t>
+          <t>1784984563</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2882,7 +2906,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>48.297994</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2895,12 +2919,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x0bf6c8f6ea5d7452bf543eb72d99a66c1b6ff74a5e56b4ad9449b6870f225d2d</t>
+          <t>0x7354c940dd56ae7caca9fa9b1a548dcf53e1a3516f531216c677cf582affb4fe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2910,12 +2934,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2942,7 +2966,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2972,7 +2996,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1784984536</t>
+          <t>1784984538</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2982,7 +3006,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>68.833427</t>
+          <t>31.184232</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2995,12 +3019,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xa4b5b4c3c3766e7d708b5373412745aa0b0d5f4c097f5451a2210d6d019269c6</t>
+          <t>0xdc3c1508859b265a9cc7ea3dadc58bb672f939bf46cde2c06081ec2891a03946</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3010,12 +3034,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -3042,7 +3066,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3072,7 +3096,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1784984502</t>
+          <t>1784984537</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3082,7 +3106,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>53.355738</t>
+          <t>48.297994</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3095,7 +3119,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xfac3960037b540d1b0b49f14ff5313d7db5bd6320c356e510ef3e6bdaca6d1ff</t>
+          <t>0x0bf6c8f6ea5d7452bf543eb72d99a66c1b6ff74a5e56b4ad9449b6870f225d2d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3110,7 +3134,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3172,7 +3196,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1784984501</t>
+          <t>1784984536</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3182,7 +3206,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>46.408957</t>
+          <t>68.833427</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3195,12 +3219,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xf3b65016998beda20548812c7503abc20be0fa3abedc59c3ac7e08e6b82c70f1</t>
+          <t>0xa4b5b4c3c3766e7d708b5373412745aa0b0d5f4c097f5451a2210d6d019269c6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3210,12 +3234,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -3242,7 +3266,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3272,7 +3296,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1784984431</t>
+          <t>1784984502</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3282,7 +3306,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>22.912332</t>
+          <t>53.355738</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3295,12 +3319,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xa04fcfb1b689fd17d1c3c66ac2ed73a6e0b99d30bdfd296529ca6549b4642440</t>
+          <t>0xfac3960037b540d1b0b49f14ff5313d7db5bd6320c356e510ef3e6bdaca6d1ff</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3310,12 +3334,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -3342,7 +3366,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3372,7 +3396,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1784984405</t>
+          <t>1784984501</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3382,7 +3406,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>60.187328</t>
+          <t>46.408957</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3395,7 +3419,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xb07983b62c387b953f021bde51a561f510162701d56466ec78a20a598c01d8c4</t>
+          <t>0xf3b65016998beda20548812c7503abc20be0fa3abedc59c3ac7e08e6b82c70f1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3410,12 +3434,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -3442,7 +3466,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3472,7 +3496,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1784984404</t>
+          <t>1784984431</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3482,7 +3506,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>60.197529</t>
+          <t>22.912332</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3495,27 +3519,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xc41db21ce0b5921299bba16424467dff9a9a6eb4d744a5aadf04422f8138f34f</t>
+          <t>0xa04fcfb1b689fd17d1c3c66ac2ed73a6e0b99d30bdfd296529ca6549b4642440</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -3542,7 +3566,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3572,7 +3596,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1784984403</t>
+          <t>1784984405</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3582,7 +3606,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>29.185737</t>
+          <t>60.187328</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3595,27 +3619,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x97d57842a441d56ad4d0172a6e2460bdd3644bd55476d419863d144ec4fb3f02</t>
+          <t>0xb07983b62c387b953f021bde51a561f510162701d56466ec78a20a598c01d8c4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -3642,7 +3666,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3672,7 +3696,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1784984403</t>
+          <t>1784984404</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3682,7 +3706,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>4.444439</t>
+          <t>60.197529</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3695,27 +3719,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x54a44d2ce4be4b546daee52057d4611c0f1d29571a9747f66b3462780e888ae0</t>
+          <t>0xc41db21ce0b5921299bba16424467dff9a9a6eb4d744a5aadf04422f8138f34f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2988</t>
+          <t>1.7712</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -3742,7 +3766,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3772,7 +3796,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1784984402</t>
+          <t>1784984403</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3782,7 +3806,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>60.178243</t>
+          <t>29.185737</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3795,27 +3819,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xf9d293335e6b1b3fd21eba9ec71cbbd6cbce398d5d606b38175d3776a077cb91</t>
+          <t>0x97d57842a441d56ad4d0172a6e2460bdd3644bd55476d419863d144ec4fb3f02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -3842,7 +3866,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xaf0827308b557ecc964e4c608c6b71f345660fa965da2a0e02882ee62ce45e49</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3872,7 +3896,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1784984401</t>
+          <t>1784984403</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3882,7 +3906,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>60.189781</t>
+          <t>4.444439</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3895,12 +3919,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x80f610f55e907d511b2c5a8d77d03f9aca143e4e50b6d7fba92997ba46481bde</t>
+          <t>0x54a44d2ce4be4b546daee52057d4611c0f1d29571a9747f66b3462780e888ae0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3910,12 +3934,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.2988</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -3942,7 +3966,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3972,7 +3996,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1784983849</t>
+          <t>1784984402</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -3982,7 +4006,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>11.988786</t>
+          <t>60.178243</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -3995,12 +4019,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x6e3d6f822ebfe70f563004b4a5a4a6303f1d1cb9677e6e3a56324cda8cc92ba7</t>
+          <t>0xf9d293335e6b1b3fd21eba9ec71cbbd6cbce398d5d606b38175d3776a077cb91</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4010,12 +4034,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -4042,7 +4066,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0xaf0827308b557ecc964e4c608c6b71f345660fa965da2a0e02882ee62ce45e49</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4072,7 +4096,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1784983797</t>
+          <t>1784984401</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4082,7 +4106,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>46.150404</t>
+          <t>60.189781</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4095,27 +4119,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
+          <t>0x80f610f55e907d511b2c5a8d77d03f9aca143e4e50b6d7fba92997ba46481bde</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -4142,7 +4166,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4172,7 +4196,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1784983703</t>
+          <t>1784983849</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4182,7 +4206,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>5.770489</t>
+          <t>11.988786</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4195,7 +4219,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
+          <t>0x6e3d6f822ebfe70f563004b4a5a4a6303f1d1cb9677e6e3a56324cda8cc92ba7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4210,7 +4234,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4272,7 +4296,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1784983703</t>
+          <t>1784983797</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4282,7 +4306,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>4.389968</t>
+          <t>46.150404</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4295,7 +4319,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x589562dc55239bfc299045a0e5bbfed420cc8f286ee7326d34ed350f83ecdd45</t>
+          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4305,17 +4329,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.7712</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -4342,7 +4366,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4372,7 +4396,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1784983480</t>
+          <t>1784983703</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4382,7 +4406,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>22.284118</t>
+          <t>5.770489</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4395,7 +4419,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x629a7bab69ed2f6eae5804065863061a8e5f95bfbf35104c3a1d130585e021ca</t>
+          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4410,7 +4434,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4472,7 +4496,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1784983361</t>
+          <t>1784983703</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4482,7 +4506,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2.228408</t>
+          <t>4.389968</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4495,12 +4519,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x888b7311174b291a1eeccf40a054d1599070da16bd2f2f7adea95d18002cc686</t>
+          <t>0x589562dc55239bfc299045a0e5bbfed420cc8f286ee7326d34ed350f83ecdd45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xB1854fc8aD8ce649EA80D007Fc67d318a239a5DA</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4510,12 +4534,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -4542,7 +4566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4572,7 +4596,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1784981088</t>
+          <t>1784983480</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4582,7 +4606,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.443442</t>
+          <t>22.284118</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4595,7 +4619,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x5d44678e836886d72dc3bddfca4b44d2be2bfa7f56096dbedd259cac92e30df3</t>
+          <t>0x629a7bab69ed2f6eae5804065863061a8e5f95bfbf35104c3a1d130585e021ca</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4605,17 +4629,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -4642,7 +4666,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4672,7 +4696,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1784981082</t>
+          <t>1784983361</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4682,7 +4706,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>21.377037</t>
+          <t>2.228408</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4695,12 +4719,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x5a96bb0ca1d506186a0e2c1c2e13d657784bbb03ad3f75e66db86da80f485bae</t>
+          <t>0x888b7311174b291a1eeccf40a054d1599070da16bd2f2f7adea95d18002cc686</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xB1854fc8aD8ce649EA80D007Fc67d318a239a5DA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4710,12 +4734,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -4742,7 +4766,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4772,7 +4796,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1784980847</t>
+          <t>1784981088</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4782,7 +4806,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>35.743728</t>
+          <t>1.443442</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4795,27 +4819,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xe6e61e0b4573e8e2199880691f7803f1943269d2b2b955ea7282a833c4dbc3c6</t>
+          <t>0x5d44678e836886d72dc3bddfca4b44d2be2bfa7f56096dbedd259cac92e30df3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.7712</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -4842,7 +4866,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4872,7 +4896,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1784977858</t>
+          <t>1784981082</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -4882,7 +4906,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>39.775279</t>
+          <t>21.377037</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -4895,12 +4919,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x668fc309ba15ebe234fe9dd2d2bf696a9f4000c9ac85f8e7d55c998a052968dc</t>
+          <t>0x5a96bb0ca1d506186a0e2c1c2e13d657784bbb03ad3f75e66db86da80f485bae</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4910,12 +4934,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -4972,7 +4996,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1784977853</t>
+          <t>1784980847</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -4982,7 +5006,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>49.797748</t>
+          <t>35.743728</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -4995,27 +5019,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xabcdef492212262464335967adbaa23c5214ede2fab0ea2a12bce6e0027067aa</t>
+          <t>0xe6e61e0b4573e8e2199880691f7803f1943269d2b2b955ea7282a833c4dbc3c6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -5042,7 +5066,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5072,7 +5096,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1784968614</t>
+          <t>1784977858</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5082,7 +5106,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>47.149425</t>
+          <t>39.775279</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5095,12 +5119,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xf7e34584abe1fc7da16770ad9dc2fe59e91a45480c1ff509d55070c7d811c7e2</t>
+          <t>0x668fc309ba15ebe234fe9dd2d2bf696a9f4000c9ac85f8e7d55c998a052968dc</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x516bfc7CE57c0E1734388ECed5Bb9454aA6aeFae</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5110,12 +5134,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -5142,7 +5166,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5172,7 +5196,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1784907257</t>
+          <t>1784977853</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5182,7 +5206,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>17.857143</t>
+          <t>49.797748</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5195,7 +5219,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x030841d8eff7e23d98d8319e71f99f9eb17cb2a743343cfac134410b86f1178e</t>
+          <t>0xabcdef492212262464335967adbaa23c5214ede2fab0ea2a12bce6e0027067aa</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5205,17 +5229,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -5242,7 +5266,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5272,7 +5296,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1784907053</t>
+          <t>1784968614</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5282,7 +5306,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>46.28739</t>
+          <t>47.149425</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5295,12 +5319,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xd486facb98ea7c7e7b67efb74b5231332788279dbd71dce40eea54aecf5d870e</t>
+          <t>0xf7e34584abe1fc7da16770ad9dc2fe59e91a45480c1ff509d55070c7d811c7e2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x516bfc7CE57c0E1734388ECed5Bb9454aA6aeFae</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5310,12 +5334,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -5342,7 +5366,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5372,7 +5396,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1784907041</t>
+          <t>1784907257</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5382,7 +5406,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>47.587302</t>
+          <t>17.857143</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5395,7 +5419,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x8a9596cb004924470885fe466db8f8d059fcb9d1b24e71490dd35bfeba65a98d</t>
+          <t>0x030841d8eff7e23d98d8319e71f99f9eb17cb2a743343cfac134410b86f1178e</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5410,12 +5434,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -5442,7 +5466,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5472,7 +5496,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1784907041</t>
+          <t>1784907053</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5482,7 +5506,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>47.555556</t>
+          <t>46.28739</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5495,7 +5519,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+          <t>0xd486facb98ea7c7e7b67efb74b5231332788279dbd71dce40eea54aecf5d870e</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5510,12 +5534,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -5542,7 +5566,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5572,7 +5596,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1784907040</t>
+          <t>1784907041</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5582,7 +5606,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>47.046509</t>
+          <t>47.587302</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5595,7 +5619,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+          <t>0x8a9596cb004924470885fe466db8f8d059fcb9d1b24e71490dd35bfeba65a98d</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5610,12 +5634,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -5642,55 +5666,255 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>47.555556</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1784907040</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>47.046509</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
         <is>
           <t>1784907040</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>1784988000</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>47.589189</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
+++ b/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xa9c4c39c3003eff066c3a4586da774f5987355742d4863d64aa5984bf9a94e7e</t>
+          <t>0xfe60d77c0d3ef99237512c490ee18191f5aa1d03dba2cab20d7b2fa662d9b510</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,19 +539,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3375</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,34 +555,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Grindavík vs Leiknir Reykjavik</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Grindavík</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Leiknir Reykjavik</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Besta Deild Karla</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Grindavík vs Leiknir Reykjavik</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Grindavík</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Leiknir Reykjavik</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
+          <t>0x427fabecbeb366a3e6cbf9174f760d871895bdec8cc17aacb1fd7361a10e941f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785298455</t>
+          <t>1785332741</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.962963</t>
+          <t>39.337474</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xee5e46dfcd55125e8c178c7b7ec5808cbc3059b6cb7c8b8db7ac3eed5d7918bc</t>
+          <t>0x7e66e5957e42e9d807368dba7d310ae682077aa4a708c192602142d5b5e26d3a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +650,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.00209</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3375</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,32 +665,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Grindavík vs Leiknir Reykjavik</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Grindavík</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Leiknir Reykjavik</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Besta Deild Karla</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Grindavík vs Leiknir Reykjavik</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Grindavík</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Leiknir Reykjavik</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
+          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785298146</t>
+          <t>1785332569</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.006193</t>
+          <t>6.925926</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xda116ce959332ba41194293702cd84c233a1aa5dc72f06cf3a812e3b16c89f50</t>
+          <t>0xabdf52be75bd88bbdb225f283ab005e92ead50197a48d25f9b85f7e3b10624be</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,12 +762,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -785,7 +777,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785267812</t>
+          <t>1785332568</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.850123</t>
+          <t>3.703704</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf8236e3ab62a3112d2d962ecd3674bb25592395a1e4e2b076102954ddd699eb7</t>
+          <t>0x53a14eddd06dd3e533c5db198fdef936dd0f80169fd35398999634473251b687</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,12 +874,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -897,24 +889,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Throttur Reykjavik</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Besta Deild Karla</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Throttur Reykjavik</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Afturelding Mosfellsbaer</t>
@@ -922,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785267777</t>
+          <t>1785330203</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785352500</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.850123</t>
+          <t>31.333333</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x9c098bbf30f27adf5fb61d9dc7cffe685f61dacbc06ffd60f2ab0ab57bf9a296</t>
+          <t>0xf28448a5cc62c9fc7b3e9b9b805707f62e0aadcfcbea022465351906ae98b144</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -994,12 +986,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1009,7 +1001,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785267742</t>
+          <t>1785328480</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2.850123</t>
+          <t>17.682243</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,27 +1083,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x4c622a3a303c2e364803ca8b5f2417b149396b0a5a454b59e42697e254ae9315</t>
+          <t>0xbe968ef03b72f6b33e82d78c222865c02cd68dfee765bbdb2b19aa9f8383edc6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.99562</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1119,26 +1107,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Throttur Reykjavik</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Besta Deild Karla</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Throttur Reykjavik</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Afturelding Mosfellsbaer</t>
@@ -1146,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0xd66bf43b2d99637498403e9a0237db2ba114292691f58bc2c9c7625d13320a22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1176,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785267709</t>
+          <t>1785328404</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785352500</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2.850123</t>
+          <t>1.502823</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,28 +1187,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x79c1f616b380c93f42fe785c942a2cc39edc55c4cdd4d5b6a09024c926a74f60</t>
+          <t>0x741d465eedb272e9a810e91b1135dcb9baa319584003652abb2eab511125d265</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.22999</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1235,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785237449</t>
+          <t>1785328404</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>20.748249</t>
+          <t>41.514894</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,28 +1291,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xce612ac2221331f875649902eb6a0cde4b9db2f0f597bbc86e7caced63d25b99</t>
+          <t>0x29749899fa54fd6426158876c5fa16e716c9033060a65217e40fae523cdd4881</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1339,27 +1323,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
+          <t>0xd66bf43b2d99637498403e9a0237db2ba114292691f58bc2c9c7625d13320a22</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1368,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785236520</t>
+          <t>1785328404</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>26.583569</t>
+          <t>1.512272</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,31 +1395,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x7ae96391e38cfe39539922631da2025b36f57f1831d5f35ec6338463f27cb2a2</t>
+          <t>0xf8a7f086c0acb7c91ab41d386c18ed5d4bb15cdf27bd96426e34ca54111ca76b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>58.82157</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1443,27 +1435,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
+          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1480,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785236069</t>
+          <t>1785328403</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.864253</t>
+          <t>235.28628</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,31 +1507,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xc979cd389b2d4ca831b9a44b7738a2ae46abf46b1bd95d0fbe5b654a09413b1e</t>
+          <t>0x89864a77b5d5ebff8c59c381b5ad542da52c6cb4c63db2003cad255d8d4f32a3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>11.00676</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1547,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
+          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785235526</t>
+          <t>1785328401</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12.353591</t>
+          <t>41.146766</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x65bc0b70a6148d6f136b1552723c33dcf058e2ee7e6097ad6d18a39367f4821b</t>
+          <t>0xca3baede79015a0cfc52cc651845c18bccee7226d69f69f10a7c75e60fcc210b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,16 +1634,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5987</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>1.2388</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1651,32 +1659,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1696,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1784987195</t>
+          <t>1785319518</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>59.090338</t>
+          <t>16.753927</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1714,35 +1722,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xd5e3b95bd82e0d7627a9203f0fe8fdd3b068e15fd373a543e05b207e66faf2a0</t>
+          <t>0xd1542fd7938e8c161366e8d42d698e01adf1463afe281cc535294abdf6bc7842</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.7862</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>1.3487</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
@@ -1751,32 +1763,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0x734f446429e4d0b08356e0ef8b2bac3a7650e770bd76d020deae31a49bbeb422</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1796,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1784986980</t>
+          <t>1785319488</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>16.327479</t>
+          <t>14.336918</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1814,35 +1826,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xbfc0a906e601c3195b374e6d33b07e4c0b0dcbf09e05e45b8bd53226678d5d88</t>
+          <t>0x62492e4a01eb77113c2e1b071ae41b105cadd04919cca89b8ca7014bc9721f89</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.7875</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>1.4175</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
@@ -1851,32 +1867,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0xd9f2f35adb6ae44e4493d055fed1654f6ffd554c49b3b528e21e86fbca64ca74</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1896,17 +1912,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1784986980</t>
+          <t>1785318340</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>47.105879</t>
+          <t>38.754491</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1914,17 +1930,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x5724a3badfc2012619fbf8e1a14ab0e7f4c66de896315371280c186505e86b85</t>
+          <t>0x6432827a2cfdbd96e9571f1efcdf14f72f570d994f1426d913f89a70ac6cc6bf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1934,16 +1954,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>3.99935</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6012</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>1.2375</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1951,32 +1979,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1996,17 +2024,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1784986978</t>
+          <t>1785316923</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>114.884008</t>
+          <t>16.839368</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2014,17 +2042,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xf825a9ec3149d5a232253fd07078e2ed75a62b287df75e59fbb6c1546f6912a3</t>
+          <t>0xe8b854d5343e46a458951fb729ff44ecdd55bbce5802e9505469ba38084b05ab</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2034,16 +2066,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2712</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>1.4338</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2051,32 +2091,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2096,17 +2136,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1784984833</t>
+          <t>1785315988</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>58.211982</t>
+          <t>32.368876</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2114,36 +2154,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
+          <t>0xde8ce086e3443091c4f5a51f73f5257cc59c68c544cb2073b7671d13aa5441e1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7887</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+          <t>1.6113</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2151,32 +2203,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x08fef34a300df073b931f351c111431efac4a9e2f9c05088229f6332fa8a17d9</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2196,17 +2248,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1785315835</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4.733718</t>
+          <t>3.337423</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2214,36 +2266,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
+          <t>0xd2abe04764d7c8cabc887d8898359d1fcd669a8bc0ac75078c4cb66acf891885</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.7887</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>1.1425</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2251,32 +2315,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x7231c5b4c0a50f911d466a47760371987199b4901dc49b546d481c4b4fea5888</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2296,17 +2360,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1785315688</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>10.745559</t>
+          <t>43.438596</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2314,17 +2378,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
+          <t>0x5fc54c4227336ff8c88052ebd8b51367babd8608caa4354840d2235f8c445ef4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2334,16 +2402,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>52.12999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5737</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+          <t>1.5962</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2351,32 +2427,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x08fef34a300df073b931f351c111431efac4a9e2f9c05088229f6332fa8a17d9</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2396,17 +2472,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1785314606</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>23.46041</t>
+          <t>87.429753</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2414,17 +2490,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x6c8964e487e133d59a699205a9a6514d54217a61ad5ca3887aa005a89c8cbdfa</t>
+          <t>0x1a1072b836045b70b8ff1ea9f263a185a2d96d90bd751aa65e7e2b8a8b95a022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2434,16 +2514,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>3.99653</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.2712</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>1.2363</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2451,32 +2539,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2496,17 +2584,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1784984810</t>
+          <t>1785313697</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>58.209253</t>
+          <t>16.916529</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2514,17 +2602,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xb8b680dda4305fed43c95dc6dbc059c9678abe5f31da65b83ac57ecd5c8d3903</t>
+          <t>0xa6a454a7ca3c8e183f6ba6e4e1e58730292bc8b254d3d62d54ea8bf3b84bcd40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2534,16 +2626,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.2712</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Grindavík 0</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2551,32 +2651,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xc9828f993aeb569543d8448a1e5c618d0c20199abfceab4e17f7ebf8bfd54e75</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2596,17 +2696,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1784984670</t>
+          <t>1785313617</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>1.927273</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2614,17 +2714,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x374cde0708e064be0b99fea4bb71434540b7ca7bbd1a444cb12a8b14c6aa3c48</t>
+          <t>0x3d27dee65048fe70c5483d5a142601c48335f0eabca1351b281cd54f33825150</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2634,16 +2738,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.2712</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>1.0962</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Völsungur</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2651,32 +2763,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2696,17 +2808,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1784984617</t>
+          <t>1785309399</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>20.779221</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2714,17 +2826,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x4c094ddc4f89a7cbd768baf6a26f7e686ead028a4b15ee75fd8f4927e1ad7989</t>
+          <t>0x1bf7465f220c7952b63c1175f884170e7e05ceb3d70a45b49968c0d14b0554dc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2734,16 +2850,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.2712</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>1.0938</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Völsungur</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2751,32 +2875,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2796,17 +2920,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1784984581</t>
+          <t>1785309399</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>21.333333</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2814,17 +2938,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x7dd8d48e4f9e00707e79d58d5900292571189d9de19bd23c6c6a9a433ea96f72</t>
+          <t>0xeabf5485d6b2e2718407dc67d4a3efe45452b6d444227f5c322d8bab91ddced4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2834,16 +2962,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>8.53999</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2712</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+          <t>1.715</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2851,32 +2987,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x656b7d09cc0a616e0e0bd68e1f6be2fe92d32e5fa76c98f6b5a315f5d570cce5</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2896,17 +3032,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1784984563</t>
+          <t>1785309398</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>11.944042</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2914,17 +3050,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x7354c940dd56ae7caca9fa9b1a548dcf53e1a3516f531216c677cf582affb4fe</t>
+          <t>0x2a502370e12bd7a2a9ef2334b42a7fbfbb726594c7309aed8cb6f1340cca9adb</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2934,16 +3074,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.3013</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Völsungur</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2951,32 +3099,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2996,17 +3144,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1784984538</t>
+          <t>1785309398</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>31.184232</t>
+          <t>20.540541</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3014,35 +3162,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xdc3c1508859b265a9cc7ea3dadc58bb672f939bf46cde2c06081ec2891a03946</t>
+          <t>0x77cf63861801098493889f49e369c4430409e1adcc4bddf5b67f53e5e59fe1ba</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>11.11999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4363</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
@@ -3051,32 +3203,32 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0x427fabecbeb366a3e6cbf9174f760d871895bdec8cc17aacb1fd7361a10e941f</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3096,17 +3248,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1784984537</t>
+          <t>1785309339</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>48.297994</t>
+          <t>18.847441</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3114,17 +3266,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x0bf6c8f6ea5d7452bf543eb72d99a66c1b6ff74a5e56b4ad9449b6870f225d2d</t>
+          <t>0x36f38c2596bcde88816f7de6ef3a9c91ee547ea55183d1ad40c996f682222c78</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3134,16 +3290,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5537</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>1.095</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Völsungur</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -3151,32 +3315,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3196,17 +3360,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1784984536</t>
+          <t>1785304871</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>68.833427</t>
+          <t>21.052632</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3214,17 +3378,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xa4b5b4c3c3766e7d708b5373412745aa0b0d5f4c097f5451a2210d6d019269c6</t>
+          <t>0x685032e5303408f01bd6b3f4d4ff212d026d08de71b76614da56e8028d7e59a5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3234,16 +3402,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5537</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>1.095</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Völsungur</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -3251,32 +3427,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3296,17 +3472,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1784984502</t>
+          <t>1785304840</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>53.355738</t>
+          <t>21.052632</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3314,17 +3490,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xfac3960037b540d1b0b49f14ff5313d7db5bd6320c356e510ef3e6bdaca6d1ff</t>
+          <t>0xa9c4c39c3003eff066c3a4586da774f5987355742d4863d64aa5984bf9a94e7e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3334,16 +3514,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5537</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+          <t>1.3375</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Leiknir Reykjavik</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -3351,32 +3539,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3396,17 +3584,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1784984501</t>
+          <t>1785298455</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>46.408957</t>
+          <t>2.962963</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3414,17 +3602,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xf3b65016998beda20548812c7503abc20be0fa3abedc59c3ac7e08e6b82c70f1</t>
+          <t>0xee5e46dfcd55125e8c178c7b7ec5808cbc3059b6cb7c8b8db7ac3eed5d7918bc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3434,16 +3626,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0.00209</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3013</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+          <t>1.3375</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leiknir Reykjavik</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -3451,32 +3651,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3496,17 +3696,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1784984431</t>
+          <t>1785298146</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>22.912332</t>
+          <t>0.006193</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3514,17 +3714,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xa04fcfb1b689fd17d1c3c66ac2ed73a6e0b99d30bdfd296529ca6549b4642440</t>
+          <t>0xda116ce959332ba41194293702cd84c233a1aa5dc72f06cf3a812e3b16c89f50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3534,16 +3738,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4537</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>1.5088</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -3551,32 +3763,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3596,17 +3808,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1784984405</t>
+          <t>1785267812</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>60.187328</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3614,17 +3826,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xb07983b62c387b953f021bde51a561f510162701d56466ec78a20a598c01d8c4</t>
+          <t>0xf8236e3ab62a3112d2d962ecd3674bb25592395a1e4e2b076102954ddd699eb7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3634,16 +3850,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.595</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>1.5088</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -3651,32 +3875,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3696,17 +3920,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1784984404</t>
+          <t>1785267777</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>60.197529</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3714,36 +3938,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xc41db21ce0b5921299bba16424467dff9a9a6eb4d744a5aadf04422f8138f34f</t>
+          <t>0x9c098bbf30f27adf5fb61d9dc7cffe685f61dacbc06ffd60f2ab0ab57bf9a296</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.7712</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+          <t>1.5088</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -3751,32 +3987,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3796,17 +4032,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1784984403</t>
+          <t>1785267742</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>29.185737</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3814,36 +4050,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x97d57842a441d56ad4d0172a6e2460bdd3644bd55476d419863d144ec4fb3f02</t>
+          <t>0x4c622a3a303c2e364803ca8b5f2417b149396b0a5a454b59e42697e254ae9315</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>1.5088</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -3851,32 +4099,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3896,17 +4144,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1784984403</t>
+          <t>1785267709</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>4.444439</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3914,35 +4162,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x54a44d2ce4be4b546daee52057d4611c0f1d29571a9747f66b3462780e888ae0</t>
+          <t>0x79c1f616b380c93f42fe785c942a2cc39edc55c4cdd4d5b6a09024c926a74f60</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>11.22999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.2988</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>1.5413</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
@@ -3951,32 +4203,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3996,17 +4248,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1784984402</t>
+          <t>1785237449</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>60.178243</t>
+          <t>20.748249</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4014,35 +4266,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xf9d293335e6b1b3fd21eba9ec71cbbd6cbce398d5d606b38175d3776a077cb91</t>
+          <t>0xce612ac2221331f875649902eb6a0cde4b9db2f0f597bbc86e7caced63d25b99</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.685</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>1.4412</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
@@ -4051,32 +4307,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xaf0827308b557ecc964e4c608c6b71f345660fa965da2a0e02882ee62ce45e49</t>
+          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -4096,17 +4352,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1784984401</t>
+          <t>1785236520</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>60.189781</t>
+          <t>26.583569</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4114,35 +4370,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x80f610f55e907d511b2c5a8d77d03f9aca143e4e50b6d7fba92997ba46481bde</t>
+          <t>0x7ae96391e38cfe39539922631da2025b36f57f1831d5f35ec6338463f27cb2a2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5537</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>1.5525</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
@@ -4151,32 +4411,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4196,17 +4456,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1784983849</t>
+          <t>1785236069</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11.988786</t>
+          <t>1.864253</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4214,35 +4474,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x6e3d6f822ebfe70f563004b4a5a4a6303f1d1cb9677e6e3a56324cda8cc92ba7</t>
+          <t>0xc979cd389b2d4ca831b9a44b7738a2ae46abf46b1bd95d0fbe5b654a09413b1e</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5513</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>1.4525</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
@@ -4251,32 +4515,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4296,17 +4560,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1784983797</t>
+          <t>1785235526</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>46.150404</t>
+          <t>12.353591</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4314,32 +4578,36 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
+          <t>0x65bc0b70a6148d6f136b1552723c33dcf058e2ee7e6097ad6d18a39367f4821b</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -4366,7 +4634,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4396,7 +4664,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1784983703</t>
+          <t>1784987195</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4406,7 +4674,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>5.770489</t>
+          <t>59.090338</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4419,7 +4687,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
+          <t>0xd5e3b95bd82e0d7627a9203f0fe8fdd3b068e15fd373a543e05b207e66faf2a0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4429,17 +4697,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.7862</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -4466,7 +4734,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4496,7 +4764,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1784983703</t>
+          <t>1784986980</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4506,7 +4774,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>4.389968</t>
+          <t>16.327479</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4519,7 +4787,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x589562dc55239bfc299045a0e5bbfed420cc8f286ee7326d34ed350f83ecdd45</t>
+          <t>0xbfc0a906e601c3195b374e6d33b07e4c0b0dcbf09e05e45b8bd53226678d5d88</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4529,17 +4797,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.7875</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -4566,7 +4834,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4596,7 +4864,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1784983480</t>
+          <t>1784986980</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4606,7 +4874,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>22.284118</t>
+          <t>47.105879</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4619,12 +4887,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x629a7bab69ed2f6eae5804065863061a8e5f95bfbf35104c3a1d130585e021ca</t>
+          <t>0x5724a3badfc2012619fbf8e1a14ab0e7f4c66de896315371280c186505e86b85</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4634,12 +4902,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.6012</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -4696,7 +4964,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1784983361</t>
+          <t>1784986978</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4706,7 +4974,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2.228408</t>
+          <t>114.884008</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4719,12 +4987,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x888b7311174b291a1eeccf40a054d1599070da16bd2f2f7adea95d18002cc686</t>
+          <t>0xf825a9ec3149d5a232253fd07078e2ed75a62b287df75e59fbb6c1546f6912a3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xB1854fc8aD8ce649EA80D007Fc67d318a239a5DA</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4734,12 +5002,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -4766,7 +5034,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4796,7 +5064,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1784981088</t>
+          <t>1784984833</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4806,7 +5074,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1.443442</t>
+          <t>58.211982</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4819,7 +5087,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x5d44678e836886d72dc3bddfca4b44d2be2bfa7f56096dbedd259cac92e30df3</t>
+          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4834,12 +5102,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -4896,7 +5164,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1784981082</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -4906,7 +5174,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>21.377037</t>
+          <t>4.733718</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -4919,7 +5187,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x5a96bb0ca1d506186a0e2c1c2e13d657784bbb03ad3f75e66db86da80f485bae</t>
+          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4929,17 +5197,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -4966,7 +5234,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4996,7 +5264,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1784980847</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5006,7 +5274,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>35.743728</t>
+          <t>10.745559</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5019,12 +5287,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xe6e61e0b4573e8e2199880691f7803f1943269d2b2b955ea7282a833c4dbc3c6</t>
+          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5034,12 +5302,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -5096,7 +5364,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1784977858</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5106,7 +5374,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>39.775279</t>
+          <t>23.46041</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5119,12 +5387,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x668fc309ba15ebe234fe9dd2d2bf696a9f4000c9ac85f8e7d55c998a052968dc</t>
+          <t>0x6c8964e487e133d59a699205a9a6514d54217a61ad5ca3887aa005a89c8cbdfa</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5134,12 +5402,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -5166,7 +5434,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5196,7 +5464,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1784977853</t>
+          <t>1784984810</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5206,7 +5474,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>49.797748</t>
+          <t>58.209253</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5219,27 +5487,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xabcdef492212262464335967adbaa23c5214ede2fab0ea2a12bce6e0027067aa</t>
+          <t>0xb8b680dda4305fed43c95dc6dbc059c9678abe5f31da65b83ac57ecd5c8d3903</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -5266,7 +5534,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5296,7 +5564,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1784968614</t>
+          <t>1784984670</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5306,7 +5574,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>47.149425</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5319,12 +5587,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xf7e34584abe1fc7da16770ad9dc2fe59e91a45480c1ff509d55070c7d811c7e2</t>
+          <t>0x374cde0708e064be0b99fea4bb71434540b7ca7bbd1a444cb12a8b14c6aa3c48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x516bfc7CE57c0E1734388ECed5Bb9454aA6aeFae</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5334,12 +5602,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -5366,7 +5634,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5396,7 +5664,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1784907257</t>
+          <t>1784984617</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5406,7 +5674,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>17.857143</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5419,12 +5687,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x030841d8eff7e23d98d8319e71f99f9eb17cb2a743343cfac134410b86f1178e</t>
+          <t>0x4c094ddc4f89a7cbd768baf6a26f7e686ead028a4b15ee75fd8f4927e1ad7989</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5434,12 +5702,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -5466,7 +5734,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5496,7 +5764,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1784907053</t>
+          <t>1784984581</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5506,7 +5774,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>46.28739</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5519,12 +5787,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xd486facb98ea7c7e7b67efb74b5231332788279dbd71dce40eea54aecf5d870e</t>
+          <t>0x7dd8d48e4f9e00707e79d58d5900292571189d9de19bd23c6c6a9a433ea96f72</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5534,12 +5802,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -5566,7 +5834,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5596,7 +5864,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1784907041</t>
+          <t>1784984563</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5606,7 +5874,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>47.587302</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5619,12 +5887,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x8a9596cb004924470885fe466db8f8d059fcb9d1b24e71490dd35bfeba65a98d</t>
+          <t>0x7354c940dd56ae7caca9fa9b1a548dcf53e1a3516f531216c677cf582affb4fe</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5634,12 +5902,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -5696,7 +5964,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1784907041</t>
+          <t>1784984538</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5706,7 +5974,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>47.555556</t>
+          <t>31.184232</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5719,7 +5987,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+          <t>0xdc3c1508859b265a9cc7ea3dadc58bb672f939bf46cde2c06081ec2891a03946</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5734,12 +6002,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -5766,7 +6034,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5796,7 +6064,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1784907040</t>
+          <t>1784984537</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -5806,7 +6074,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>47.046509</t>
+          <t>48.297994</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -5819,12 +6087,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+          <t>0x0bf6c8f6ea5d7452bf543eb72d99a66c1b6ff74a5e56b4ad9449b6870f225d2d</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5834,12 +6102,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -5866,55 +6134,2755 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1784984536</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>68.833427</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0xa4b5b4c3c3766e7d708b5373412745aa0b0d5f4c097f5451a2210d6d019269c6</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.5537</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1784984502</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>53.355738</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0xfac3960037b540d1b0b49f14ff5313d7db5bd6320c356e510ef3e6bdaca6d1ff</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.5537</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1784984501</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>46.408957</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0xf3b65016998beda20548812c7503abc20be0fa3abedc59c3ac7e08e6b82c70f1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.3013</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1784984431</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>22.912332</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0xa04fcfb1b689fd17d1c3c66ac2ed73a6e0b99d30bdfd296529ca6549b4642440</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.4537</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1784984405</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>60.187328</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0xb07983b62c387b953f021bde51a561f510162701d56466ec78a20a598c01d8c4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1784984404</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>60.197529</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0xc41db21ce0b5921299bba16424467dff9a9a6eb4d744a5aadf04422f8138f34f</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.7712</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1784984403</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>29.185737</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x97d57842a441d56ad4d0172a6e2460bdd3644bd55476d419863d144ec4fb3f02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1784984403</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>4.444439</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x54a44d2ce4be4b546daee52057d4611c0f1d29571a9747f66b3462780e888ae0</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.2988</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1784984402</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>60.178243</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0xf9d293335e6b1b3fd21eba9ec71cbbd6cbce398d5d606b38175d3776a077cb91</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.685</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xaf0827308b557ecc964e4c608c6b71f345660fa965da2a0e02882ee62ce45e49</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1784984401</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>60.189781</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x80f610f55e907d511b2c5a8d77d03f9aca143e4e50b6d7fba92997ba46481bde</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.5537</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1784983849</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>11.988786</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x6e3d6f822ebfe70f563004b4a5a4a6303f1d1cb9677e6e3a56324cda8cc92ba7</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1784983797</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>46.150404</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.7712</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1784983703</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>5.770489</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1784983703</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>4.389968</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x589562dc55239bfc299045a0e5bbfed420cc8f286ee7326d34ed350f83ecdd45</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1784983480</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>22.284118</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x629a7bab69ed2f6eae5804065863061a8e5f95bfbf35104c3a1d130585e021ca</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1784983361</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2.228408</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x888b7311174b291a1eeccf40a054d1599070da16bd2f2f7adea95d18002cc686</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0xB1854fc8aD8ce649EA80D007Fc67d318a239a5DA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.215</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1784981088</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1.443442</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x5d44678e836886d72dc3bddfca4b44d2be2bfa7f56096dbedd259cac92e30df3</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.7712</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1784981082</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>21.377037</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x5a96bb0ca1d506186a0e2c1c2e13d657784bbb03ad3f75e66db86da80f485bae</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1784980847</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>35.743728</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0xe6e61e0b4573e8e2199880691f7803f1943269d2b2b955ea7282a833c4dbc3c6</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1784977858</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>39.775279</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0x668fc309ba15ebe234fe9dd2d2bf696a9f4000c9ac85f8e7d55c998a052968dc</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1784977853</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>49.797748</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0xabcdef492212262464335967adbaa23c5214ede2fab0ea2a12bce6e0027067aa</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.435</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1784968614</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>47.149425</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xf7e34584abe1fc7da16770ad9dc2fe59e91a45480c1ff509d55070c7d811c7e2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0x516bfc7CE57c0E1734388ECed5Bb9454aA6aeFae</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1784907257</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>17.857143</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0x030841d8eff7e23d98d8319e71f99f9eb17cb2a743343cfac134410b86f1178e</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.5737</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1784907053</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>46.28739</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0xd486facb98ea7c7e7b67efb74b5231332788279dbd71dce40eea54aecf5d870e</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>47.587302</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0x8a9596cb004924470885fe466db8f8d059fcb9d1b24e71490dd35bfeba65a98d</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>47.555556</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
         <is>
           <t>1784907040</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>1784988000</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>47.046509</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1784907040</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
         <is>
           <t>47.589189</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
+++ b/data/sxbet/ligas/Besta Deild Karla/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xfe60d77c0d3ef99237512c490ee18191f5aa1d03dba2cab20d7b2fa662d9b510</t>
+          <t>0x4aff3ba015f4d5f826957b8c1b48f7d832e99fb9b0c94c3d13a7c942c249b64b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,23 +539,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fylkir -3.5</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Grindavík vs Leiknir Reykjavik</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Grindavík</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x427fabecbeb366a3e6cbf9174f760d871895bdec8cc17aacb1fd7361a10e941f</t>
+          <t>0x0876c4a6828dc69b9f0c780112f629d94e837b63718d4e072cedf6261ca2f05a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19558553</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785332741</t>
+          <t>1785344451</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785352500</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>39.337474</t>
+          <t>60.166667</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7e66e5957e42e9d807368dba7d310ae682077aa4a708c192602142d5b5e26d3a</t>
+          <t>0xe32c51ac474d570481983f944ea2eeaa72b52cbf5e4dbaa5b7b34e7099ab3f14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>16.20769</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Fylkir -2.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Grindavík vs Leiknir Reykjavik</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Grindavík</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
+          <t>0xbd9f66ad57237507cf428f594d6d114c399e0464940c27c4aef80ac029bf8ca1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19558553</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785332569</t>
+          <t>1785344449</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785352500</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6.925926</t>
+          <t>46.307686</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,39 +755,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xabdf52be75bd88bbdb225f283ab005e92ead50197a48d25f9b85f7e3b10624be</t>
+          <t>0x1144bece84353bf243f2e74e1f34ad40a046d345e525c8813541f4a2b77b671c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29.11596</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.6288</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Grindavík vs Leiknir Reykjavik</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Grindavík</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
+          <t>0xbd9f66ad57237507cf428f594d6d114c399e0464940c27c4aef80ac029bf8ca1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19558553</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785332568</t>
+          <t>1785344448</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785352500</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.703704</t>
+          <t>46.30769</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x53a14eddd06dd3e533c5db198fdef936dd0f80169fd35398999634473251b687</t>
+          <t>0x073c2c43c3ca748be54a92e0b26c5f28d90130614d20b6c01151e85eae169565</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>26.70877</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Fylkir -2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
+          <t>0xdc8c5652ca6e8a5736c2dba125c81d59df51a53d9c5a64b5cda8753a2447f188</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785330203</t>
+          <t>1785344446</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785354300</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>31.333333</t>
+          <t>60.188777</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xf28448a5cc62c9fc7b3e9b9b805707f62e0aadcfcbea022465351906ae98b144</t>
+          <t>0xaccc10d9ffefd8df8ae527da66cf5c9275b95d79e56b9fc76725ecb38cfec32b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Grindavík vs Leiknir Reykjavik</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Grindavík</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
+          <t>0x08fef34a300df073b931f351c111431efac4a9e2f9c05088229f6332fa8a17d9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19558553</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785328480</t>
+          <t>1785344436</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785352500</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>17.682243</t>
+          <t>60.189655</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xbe968ef03b72f6b33e82d78c222865c02cd68dfee765bbdb2b19aa9f8383edc6</t>
+          <t>0x7308736f412c4e30d6aaf4dd32d85a406da0e5d36beb2eabf31b9a22cb035612</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1091,23 +1091,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99562</t>
+          <t>26.70877</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.6625</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fylkir -2</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1115,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd66bf43b2d99637498403e9a0237db2ba114292691f58bc2c9c7625d13320a22</t>
+          <t>0xdc8c5652ca6e8a5736c2dba125c81d59df51a53d9c5a64b5cda8753a2447f188</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785328404</t>
+          <t>1785344422</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785354300</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.502823</t>
+          <t>60.188777</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x741d465eedb272e9a810e91b1135dcb9baa319584003652abb2eab511125d265</t>
+          <t>0xdc3283ad1a88e9f4c26f9b4b71da1b70924a2957a38ab8f28bd7d6fb9d216e2f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1195,23 +1203,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fylkir -3.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1219,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0x0876c4a6828dc69b9f0c780112f629d94e837b63718d4e072cedf6261ca2f05a</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785328404</t>
+          <t>1785344421</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785354300</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>41.514894</t>
+          <t>60.166667</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x29749899fa54fd6426158876c5fa16e716c9033060a65217e40fae523cdd4881</t>
+          <t>0x5902ea166c43507387debc5d8cc0c78b2b040e041aa4bfdb4c1f314b057281c0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1299,15 +1315,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1315,7 +1335,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leiknir Reykjavik</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1323,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd66bf43b2d99637498403e9a0237db2ba114292691f58bc2c9c7625d13320a22</t>
+          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785328404</t>
+          <t>1785341700</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785354300</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.512272</t>
+          <t>4.483516</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,39 +1419,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xf8a7f086c0acb7c91ab41d386c18ed5d4bb15cdf27bd96426e34ca54111ca76b</t>
+          <t>0x887bb80242ed960eae29e242a4f7d68771cc24a52fed088c888075011aae89e0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7798905FEB7e16ae299D9F0Ab8B294084EF92B58</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>58.82157</t>
+          <t>222</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1450,7 +1466,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
+          <t>0x202e2e81d1f89091b83b5bf504582d86de63fcfdd756f909ca3c6652d05ab86b</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785328403</t>
+          <t>1785336076</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>235.28628</t>
+          <t>486.575342</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x89864a77b5d5ebff8c59c381b5ad542da52c6cb4c63db2003cad255d8d4f32a3</t>
+          <t>0xa5e461e0e59c6692085244a79f12890d3da3ddd6439b27fe7e25296bce8ceb41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1515,19 +1531,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.00676</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1535,11 +1547,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1562,7 +1570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
+          <t>0x427fabecbeb366a3e6cbf9174f760d871895bdec8cc17aacb1fd7361a10e941f</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785328401</t>
+          <t>1785334472</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>41.146766</t>
+          <t>1.656315</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xca3baede79015a0cfc52cc651845c18bccee7226d69f69f10a7c75e60fcc210b</t>
+          <t>0x6f04b22e07213877efece2d24c48f3e3c0f065f4eec720e46a34767048b8ad86</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1627,19 +1635,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2388</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1647,11 +1651,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1659,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
+          <t>0x427fabecbeb366a3e6cbf9174f760d871895bdec8cc17aacb1fd7361a10e941f</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785319518</t>
+          <t>1785334472</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785354300</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>16.753927</t>
+          <t>1.656315</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,28 +1731,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xd1542fd7938e8c161366e8d42d698e01adf1463afe281cc535294abdf6bc7842</t>
+          <t>0xfe60d77c0d3ef99237512c490ee18191f5aa1d03dba2cab20d7b2fa662d9b510</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3487</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1763,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x734f446429e4d0b08356e0ef8b2bac3a7650e770bd76d020deae31a49bbeb422</t>
+          <t>0x427fabecbeb366a3e6cbf9174f760d871895bdec8cc17aacb1fd7361a10e941f</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1808,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785319488</t>
+          <t>1785332741</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785354300</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>14.336918</t>
+          <t>39.337474</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,31 +1835,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x62492e4a01eb77113c2e1b071ae41b105cadd04919cca89b8ca7014bc9721f89</t>
+          <t>0x7e66e5957e42e9d807368dba7d310ae682077aa4a708c192602142d5b5e26d3a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -1882,7 +1890,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd9f2f35adb6ae44e4493d055fed1654f6ffd554c49b3b528e21e86fbca64ca74</t>
+          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785318340</t>
+          <t>1785332569</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>38.754491</t>
+          <t>6.925926</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,7 +1947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x6432827a2cfdbd96e9571f1efcdf14f72f570d994f1426d913f89a70ac6cc6bf</t>
+          <t>0xabdf52be75bd88bbdb225f283ab005e92ead50197a48d25f9b85f7e3b10624be</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1954,12 +1962,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.99935</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2375</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1979,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
+          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2024,17 +2032,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785316923</t>
+          <t>1785332568</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785354300</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>16.839368</t>
+          <t>3.703704</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,12 +2059,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xe8b854d5343e46a458951fb729ff44ecdd55bbce5802e9505469ba38084b05ab</t>
+          <t>0x53a14eddd06dd3e533c5db198fdef936dd0f80169fd35398999634473251b687</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2066,12 +2074,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2081,24 +2089,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>Throttur Reykjavik</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Besta Deild Karla</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Throttur Reykjavik</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Afturelding Mosfellsbaer</t>
@@ -2106,7 +2114,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2136,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785315988</t>
+          <t>1785330203</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2146,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>32.368876</t>
+          <t>31.333333</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,12 +2171,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xde8ce086e3443091c4f5a51f73f5257cc59c68c544cb2073b7671d13aa5441e1</t>
+          <t>0xf28448a5cc62c9fc7b3e9b9b805707f62e0aadcfcbea022465351906ae98b144</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2178,22 +2186,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2203,27 +2211,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Fylkir vs Völsungur</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x08fef34a300df073b931f351c111431efac4a9e2f9c05088229f6332fa8a17d9</t>
+          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19558540</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2248,17 +2256,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785315835</t>
+          <t>1785328480</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785348000</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3.337423</t>
+          <t>17.682243</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,27 +2283,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xd2abe04764d7c8cabc887d8898359d1fcd669a8bc0ac75078c4cb66acf891885</t>
+          <t>0xbe968ef03b72f6b33e82d78c222865c02cd68dfee765bbdb2b19aa9f8383edc6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>0.99562</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.1425</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2303,11 +2307,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2315,27 +2315,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Fylkir vs Völsungur</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x7231c5b4c0a50f911d466a47760371987199b4901dc49b546d481c4b4fea5888</t>
+          <t>0xd66bf43b2d99637498403e9a0237db2ba114292691f58bc2c9c7625d13320a22</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19558540</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785315688</t>
+          <t>1785328404</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785348000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>43.438596</t>
+          <t>1.502823</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,39 +2387,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x5fc54c4227336ff8c88052ebd8b51367babd8608caa4354840d2235f8c445ef4</t>
+          <t>0x741d465eedb272e9a810e91b1135dcb9baa319584003652abb2eab511125d265</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.12999</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2427,27 +2419,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Fylkir vs Völsungur</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x08fef34a300df073b931f351c111431efac4a9e2f9c05088229f6332fa8a17d9</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19558540</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2472,17 +2464,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785314606</t>
+          <t>1785328404</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785348000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>87.429753</t>
+          <t>41.514894</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,7 +2491,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x1a1072b836045b70b8ff1ea9f263a185a2d96d90bd751aa65e7e2b8a8b95a022</t>
+          <t>0x29749899fa54fd6426158876c5fa16e716c9033060a65217e40fae523cdd4881</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2507,19 +2499,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.99653</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.2363</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2527,11 +2515,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2554,7 +2538,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
+          <t>0xd66bf43b2d99637498403e9a0237db2ba114292691f58bc2c9c7625d13320a22</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2584,7 +2568,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785313697</t>
+          <t>1785328404</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2594,7 +2578,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>16.916529</t>
+          <t>1.512272</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2611,12 +2595,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xa6a454a7ca3c8e183f6ba6e4e1e58730292bc8b254d3d62d54ea8bf3b84bcd40</t>
+          <t>0xf8a7f086c0acb7c91ab41d386c18ed5d4bb15cdf27bd96426e34ca54111ca76b</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2626,52 +2610,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>58.82157</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>Besta Deild Karla</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Grindavík 0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Besta Deild Karla</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Grindavík vs Leiknir Reykjavik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Grindavík</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xc9828f993aeb569543d8448a1e5c618d0c20199abfceab4e17f7ebf8bfd54e75</t>
+          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19558553</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2696,17 +2680,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785313617</t>
+          <t>1785328403</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785352500</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.927273</t>
+          <t>235.28628</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2723,7 +2707,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x3d27dee65048fe70c5483d5a142601c48335f0eabca1351b281cd54f33825150</t>
+          <t>0x89864a77b5d5ebff8c59c381b5ad542da52c6cb4c63db2003cad255d8d4f32a3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2738,12 +2722,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11.00676</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2753,7 +2737,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2763,27 +2747,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Fylkir vs Völsungur</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
+          <t>0x4b9c3737e2afb486edaff0ed23cce8d71af9bbfcd593a790243e5fc471ec6133</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19558540</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2808,17 +2792,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785309399</t>
+          <t>1785328401</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785348000</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>20.779221</t>
+          <t>41.146766</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2835,7 +2819,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x1bf7465f220c7952b63c1175f884170e7e05ceb3d70a45b49968c0d14b0554dc</t>
+          <t>0xca3baede79015a0cfc52cc651845c18bccee7226d69f69f10a7c75e60fcc210b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2850,12 +2834,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.2388</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2865,7 +2849,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2875,27 +2859,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Fylkir vs Völsungur</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
+          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19558540</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2920,17 +2904,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785309399</t>
+          <t>1785319518</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785348000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>21.333333</t>
+          <t>16.753927</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2947,39 +2931,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xeabf5485d6b2e2718407dc67d4a3efe45452b6d444227f5c322d8bab91ddced4</t>
+          <t>0xd1542fd7938e8c161366e8d42d698e01adf1463afe281cc535294abdf6bc7842</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.53999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -2987,27 +2963,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Fylkir vs Völsungur</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x656b7d09cc0a616e0e0bd68e1f6be2fe92d32e5fa76c98f6b5a315f5d570cce5</t>
+          <t>0x734f446429e4d0b08356e0ef8b2bac3a7650e770bd76d020deae31a49bbeb422</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19558540</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3032,17 +3008,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785309398</t>
+          <t>1785319488</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785348000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>11.944042</t>
+          <t>14.336918</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3059,39 +3035,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x2a502370e12bd7a2a9ef2334b42a7fbfbb726594c7309aed8cb6f1340cca9adb</t>
+          <t>0x62492e4a01eb77113c2e1b071ae41b105cadd04919cca89b8ca7014bc9721f89</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Völsungur</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -3099,27 +3067,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Fylkir vs Völsungur</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
+          <t>0xd9f2f35adb6ae44e4493d055fed1654f6ffd554c49b3b528e21e86fbca64ca74</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19558540</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3144,17 +3112,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785309398</t>
+          <t>1785318340</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785348000</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>20.540541</t>
+          <t>38.754491</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3171,7 +3139,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x77cf63861801098493889f49e369c4430409e1adcc4bddf5b67f53e5e59fe1ba</t>
+          <t>0x6432827a2cfdbd96e9571f1efcdf14f72f570d994f1426d913f89a70ac6cc6bf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3179,15 +3147,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11.11999</t>
+          <t>3.99935</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.2375</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3195,7 +3167,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -3203,27 +3179,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Grindavík vs Leiknir Reykjavik</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Grindavík</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x427fabecbeb366a3e6cbf9174f760d871895bdec8cc17aacb1fd7361a10e941f</t>
+          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19558553</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3248,17 +3224,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785309339</t>
+          <t>1785316923</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785352500</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>18.847441</t>
+          <t>16.839368</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3275,12 +3251,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x36f38c2596bcde88816f7de6ef3a9c91ee547ea55183d1ad40c996f682222c78</t>
+          <t>0xe8b854d5343e46a458951fb729ff44ecdd55bbce5802e9505469ba38084b05ab</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3290,12 +3266,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.095</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3305,7 +3281,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3315,27 +3291,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Fylkir vs Völsungur</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Völsungur</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19558540</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3360,17 +3336,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785304871</t>
+          <t>1785315988</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785348000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>21.052632</t>
+          <t>32.368876</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3387,12 +3363,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x685032e5303408f01bd6b3f4d4ff212d026d08de71b76614da56e8028d7e59a5</t>
+          <t>0xde8ce086e3443091c4f5a51f73f5257cc59c68c544cb2073b7671d13aa5441e1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3402,47 +3378,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.095</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Fylkir vs Völsungur</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>Völsungur</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Besta Deild Karla</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Fylkir vs Völsungur</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Fylkir</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Völsungur</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
+          <t>0x08fef34a300df073b931f351c111431efac4a9e2f9c05088229f6332fa8a17d9</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3472,7 +3448,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785304840</t>
+          <t>1785315835</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3482,7 +3458,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>21.052632</t>
+          <t>3.337423</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3499,12 +3475,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xa9c4c39c3003eff066c3a4586da774f5987355742d4863d64aa5984bf9a94e7e</t>
+          <t>0xd2abe04764d7c8cabc887d8898359d1fcd669a8bc0ac75078c4cb66acf891885</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3514,12 +3490,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3375</t>
+          <t>1.1425</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3529,7 +3505,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3539,27 +3515,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Grindavík vs Leiknir Reykjavik</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Grindavík</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
+          <t>0x7231c5b4c0a50f911d466a47760371987199b4901dc49b546d481c4b4fea5888</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19558553</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3584,17 +3560,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785298455</t>
+          <t>1785315688</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785352500</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2.962963</t>
+          <t>43.438596</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3611,12 +3587,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xee5e46dfcd55125e8c178c7b7ec5808cbc3059b6cb7c8b8db7ac3eed5d7918bc</t>
+          <t>0x5fc54c4227336ff8c88052ebd8b51367babd8608caa4354840d2235f8c445ef4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3626,22 +3602,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.00209</t>
+          <t>52.12999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3375</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3651,27 +3627,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Grindavík vs Leiknir Reykjavik</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Grindavík</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
+          <t>0x08fef34a300df073b931f351c111431efac4a9e2f9c05088229f6332fa8a17d9</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19558553</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3696,17 +3672,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785298146</t>
+          <t>1785314606</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785352500</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.006193</t>
+          <t>87.429753</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3723,12 +3699,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xda116ce959332ba41194293702cd84c233a1aa5dc72f06cf3a812e3b16c89f50</t>
+          <t>0x1a1072b836045b70b8ff1ea9f263a185a2d96d90bd751aa65e7e2b8a8b95a022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3738,12 +3714,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.99653</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.2363</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3753,24 +3729,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>Throttur Reykjavik</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Besta Deild Karla</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Throttur Reykjavik</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Afturelding Mosfellsbaer</t>
@@ -3778,7 +3754,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0x15cee278a15db9f03be3b6f65f860826616c47bd2de7537d12a9ed01942a533c</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3808,7 +3784,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785267812</t>
+          <t>1785313697</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3818,7 +3794,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2.850123</t>
+          <t>16.916529</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3835,12 +3811,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf8236e3ab62a3112d2d962ecd3674bb25592395a1e4e2b076102954ddd699eb7</t>
+          <t>0xa6a454a7ca3c8e183f6ba6e4e1e58730292bc8b254d3d62d54ea8bf3b84bcd40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3850,22 +3826,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Besta Deild Karla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Grindavík 0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3875,27 +3851,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0xc9828f993aeb569543d8448a1e5c618d0c20199abfceab4e17f7ebf8bfd54e75</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3920,17 +3896,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785267777</t>
+          <t>1785313617</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785354300</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.850123</t>
+          <t>1.927273</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3947,12 +3923,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x9c098bbf30f27adf5fb61d9dc7cffe685f61dacbc06ffd60f2ab0ab57bf9a296</t>
+          <t>0x3d27dee65048fe70c5483d5a142601c48335f0eabca1351b281cd54f33825150</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3962,12 +3938,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3977,7 +3953,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3987,27 +3963,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4032,17 +4008,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785267742</t>
+          <t>1785309399</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785354300</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2.850123</t>
+          <t>20.779221</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4059,12 +4035,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x4c622a3a303c2e364803ca8b5f2417b149396b0a5a454b59e42697e254ae9315</t>
+          <t>0x1bf7465f220c7952b63c1175f884170e7e05ceb3d70a45b49968c0d14b0554dc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4074,12 +4050,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4089,7 +4065,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4099,27 +4075,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Afturelding Mosfellsbaer</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
+          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19558554</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4144,17 +4120,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785267709</t>
+          <t>1785309399</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785354300</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2.850123</t>
+          <t>21.333333</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4171,31 +4147,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x79c1f616b380c93f42fe785c942a2cc39edc55c4cdd4d5b6a09024c926a74f60</t>
+          <t>0xeabf5485d6b2e2718407dc67d4a3efe45452b6d444227f5c322d8bab91ddced4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>11.22999</t>
+          <t>8.53999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.715</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -4203,27 +4187,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
+          <t>0x656b7d09cc0a616e0e0bd68e1f6be2fe92d32e5fa76c98f6b5a315f5d570cce5</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4248,17 +4232,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785237449</t>
+          <t>1785309398</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>20.748249</t>
+          <t>11.944042</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4275,31 +4259,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xce612ac2221331f875649902eb6a0cde4b9db2f0f597bbc86e7caced63d25b99</t>
+          <t>0x2a502370e12bd7a2a9ef2334b42a7fbfbb726594c7309aed8cb6f1340cca9adb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.0925</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Völsungur</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -4307,27 +4299,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
+          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4352,17 +4344,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785236520</t>
+          <t>1785309398</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>26.583569</t>
+          <t>20.540541</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4379,28 +4371,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x7ae96391e38cfe39539922631da2025b36f57f1831d5f35ec6338463f27cb2a2</t>
+          <t>0x77cf63861801098493889f49e369c4430409e1adcc4bddf5b67f53e5e59fe1ba</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>11.11999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4411,27 +4403,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
+          <t>0x427fabecbeb366a3e6cbf9174f760d871895bdec8cc17aacb1fd7361a10e941f</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4456,17 +4448,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785236069</t>
+          <t>1785309339</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.864253</t>
+          <t>18.847441</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4483,31 +4475,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xc979cd389b2d4ca831b9a44b7738a2ae46abf46b1bd95d0fbe5b654a09413b1e</t>
+          <t>0x36f38c2596bcde88816f7de6ef3a9c91ee547ea55183d1ad40c996f682222c78</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.095</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Völsungur</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -4515,27 +4515,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Aegir vs Njardvik</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
+          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19548408</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4560,17 +4560,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785235526</t>
+          <t>1785304871</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785266100</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>12.353591</t>
+          <t>21.052632</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4587,12 +4587,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x65bc0b70a6148d6f136b1552723c33dcf058e2ee7e6097ad6d18a39367f4821b</t>
+          <t>0x685032e5303408f01bd6b3f4d4ff212d026d08de71b76614da56e8028d7e59a5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4602,16 +4602,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5987</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>1.095</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Völsungur</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -4619,32 +4627,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Fylkir vs Völsungur</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Völsungur</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+          <t>0x8435d458712b11d97a656bb42d972a163c4e819e03559a7700255d228fbca381</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558540</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4664,17 +4672,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1784987195</t>
+          <t>1785304840</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>59.090338</t>
+          <t>21.052632</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4682,36 +4690,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xd5e3b95bd82e0d7627a9203f0fe8fdd3b068e15fd373a543e05b207e66faf2a0</t>
+          <t>0xa9c4c39c3003eff066c3a4586da774f5987355742d4863d64aa5984bf9a94e7e</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.7862</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+          <t>1.3375</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Leiknir Reykjavik</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -4719,32 +4739,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4764,17 +4784,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1784986980</t>
+          <t>1785298455</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>16.327479</t>
+          <t>2.962963</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4782,36 +4802,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xbfc0a906e601c3195b374e6d33b07e4c0b0dcbf09e05e45b8bd53226678d5d88</t>
+          <t>0xee5e46dfcd55125e8c178c7b7ec5808cbc3059b6cb7c8b8db7ac3eed5d7918bc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>0.00209</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.7875</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>1.3375</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Leiknir Reykjavik</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -4819,32 +4851,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Grindavík vs Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Grindavík</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0xa483946547c248863e7e21964d2b27f06ba27a90ee1332f03f91f58c894d0ab5</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558553</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4864,17 +4896,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1784986980</t>
+          <t>1785298146</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785352500</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>47.105879</t>
+          <t>0.006193</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4882,17 +4914,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x5724a3badfc2012619fbf8e1a14ab0e7f4c66de896315371280c186505e86b85</t>
+          <t>0xda116ce959332ba41194293702cd84c233a1aa5dc72f06cf3a812e3b16c89f50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4902,16 +4938,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.6012</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>1.5088</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -4919,32 +4963,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4964,17 +5008,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1784986978</t>
+          <t>1785267812</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>114.884008</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4982,17 +5026,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xf825a9ec3149d5a232253fd07078e2ed75a62b287df75e59fbb6c1546f6912a3</t>
+          <t>0xf8236e3ab62a3112d2d962ecd3674bb25592395a1e4e2b076102954ddd699eb7</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5002,16 +5050,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.2712</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+          <t>1.5088</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -5019,32 +5075,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -5064,17 +5120,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1784984833</t>
+          <t>1785267777</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>58.211982</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5082,36 +5138,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
+          <t>0x9c098bbf30f27adf5fb61d9dc7cffe685f61dacbc06ffd60f2ab0ab57bf9a296</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7887</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>1.5088</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -5119,32 +5187,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -5164,17 +5232,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1785267742</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>4.733718</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5182,36 +5250,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
+          <t>0x4c622a3a303c2e364803ca8b5f2417b149396b0a5a454b59e42697e254ae9315</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x5A76a26f838Ff5430Fd53E61CD8Bd76D895c946E</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.7887</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+          <t>1.5088</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Besta Deild Karla</t>
@@ -5219,32 +5299,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Throttur Reykjavik vs Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding Mosfellsbaer</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x7a5019973da533d172cf682264ba4b7ae8b6e65bb7591585a6fce73a807f64b0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19558554</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -5264,17 +5344,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1785267709</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785354300</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>10.745559</t>
+          <t>2.850123</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5282,35 +5362,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
+          <t>0x79c1f616b380c93f42fe785c942a2cc39edc55c4cdd4d5b6a09024c926a74f60</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>11.22999</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5737</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>1.5413</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
@@ -5319,32 +5403,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -5364,17 +5448,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1784984812</t>
+          <t>1785237449</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>23.46041</t>
+          <t>20.748249</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5382,35 +5466,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x6c8964e487e133d59a699205a9a6514d54217a61ad5ca3887aa005a89c8cbdfa</t>
+          <t>0xce612ac2221331f875649902eb6a0cde4b9db2f0f597bbc86e7caced63d25b99</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.2712</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>1.4412</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
@@ -5419,32 +5507,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5464,17 +5552,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1784984810</t>
+          <t>1785236520</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>58.209253</t>
+          <t>26.583569</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5482,35 +5570,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xb8b680dda4305fed43c95dc6dbc059c9678abe5f31da65b83ac57ecd5c8d3903</t>
+          <t>0x7ae96391e38cfe39539922631da2025b36f57f1831d5f35ec6338463f27cb2a2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.2712</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>1.5525</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
@@ -5519,32 +5611,32 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xde9c2677ae0e84c01c06a23050c75f29399db6bd766b2ef90484b73f8e0bbaed</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -5564,17 +5656,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1784984670</t>
+          <t>1785236069</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>1.864253</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5582,35 +5674,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x374cde0708e064be0b99fea4bb71434540b7ca7bbd1a444cb12a8b14c6aa3c48</t>
+          <t>0xc979cd389b2d4ca831b9a44b7738a2ae46abf46b1bd95d0fbe5b654a09413b1e</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.2712</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>1.4525</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
@@ -5619,32 +5715,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>IR Reykjavik vs Fylkir</t>
+          <t>Aegir vs Njardvik</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x0825c99784fd72c055ffaeeb62e8e792f152ccd5a39c675722acf968b754f571</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19520873</t>
+          <t>L19548408</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5664,17 +5760,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1784984617</t>
+          <t>1785235526</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1784988000</t>
+          <t>1785266100</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>12.353591</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5682,12 +5778,16 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x4c094ddc4f89a7cbd768baf6a26f7e686ead028a4b15ee75fd8f4927e1ad7989</t>
+          <t>0x65bc0b70a6148d6f136b1552723c33dcf058e2ee7e6097ad6d18a39367f4821b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5702,12 +5802,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -5734,7 +5834,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5764,7 +5864,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1784984581</t>
+          <t>1784987195</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5774,7 +5874,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>59.090338</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5787,27 +5887,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x7dd8d48e4f9e00707e79d58d5900292571189d9de19bd23c6c6a9a433ea96f72</t>
+          <t>0xd5e3b95bd82e0d7627a9203f0fe8fdd3b068e15fd373a543e05b207e66faf2a0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.2712</t>
+          <t>1.7862</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -5834,7 +5934,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5864,7 +5964,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1784984563</t>
+          <t>1784986980</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5874,7 +5974,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>60.198968</t>
+          <t>16.327479</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5887,27 +5987,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x7354c940dd56ae7caca9fa9b1a548dcf53e1a3516f531216c677cf582affb4fe</t>
+          <t>0xbfc0a906e601c3195b374e6d33b07e4c0b0dcbf09e05e45b8bd53226678d5d88</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.7875</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -5934,7 +6034,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5964,7 +6064,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1784984538</t>
+          <t>1784986980</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5974,7 +6074,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>31.184232</t>
+          <t>47.105879</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5987,12 +6087,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xdc3c1508859b265a9cc7ea3dadc58bb672f939bf46cde2c06081ec2891a03946</t>
+          <t>0x5724a3badfc2012619fbf8e1a14ab0e7f4c66de896315371280c186505e86b85</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6002,12 +6102,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.6012</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -6034,7 +6134,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6064,7 +6164,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1784984537</t>
+          <t>1784986978</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6074,7 +6174,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>48.297994</t>
+          <t>114.884008</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6087,12 +6187,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x0bf6c8f6ea5d7452bf543eb72d99a66c1b6ff74a5e56b4ad9449b6870f225d2d</t>
+          <t>0xf825a9ec3149d5a232253fd07078e2ed75a62b287df75e59fbb6c1546f6912a3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6102,12 +6202,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -6134,7 +6234,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6164,7 +6264,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1784984536</t>
+          <t>1784984833</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6174,7 +6274,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>68.833427</t>
+          <t>58.211982</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6187,27 +6287,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xa4b5b4c3c3766e7d708b5373412745aa0b0d5f4c097f5451a2210d6d019269c6</t>
+          <t>0x832d570bfcb61240d74893710e1758118ea62888a2bf55921f3190b9a71f4561</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -6234,7 +6334,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6264,7 +6364,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1784984502</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6274,7 +6374,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>53.355738</t>
+          <t>4.733718</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6287,27 +6387,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xfac3960037b540d1b0b49f14ff5313d7db5bd6320c356e510ef3e6bdaca6d1ff</t>
+          <t>0x78e73a1fbc4bce58e1469ba84a7a75afedee1c817a9927ff72cae6f55f5b4a58</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.7887</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -6334,7 +6434,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6364,7 +6464,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1784984501</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6374,7 +6474,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>46.408957</t>
+          <t>10.745559</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6387,12 +6487,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xf3b65016998beda20548812c7503abc20be0fa3abedc59c3ac7e08e6b82c70f1</t>
+          <t>0x02053d570c2ec6485bf734b3e9d25cb6962b678b5212cc142c9b62d371752a01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6402,12 +6502,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -6434,7 +6534,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6464,7 +6564,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1784984431</t>
+          <t>1784984812</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6474,7 +6574,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>22.912332</t>
+          <t>23.46041</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6487,7 +6587,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xa04fcfb1b689fd17d1c3c66ac2ed73a6e0b99d30bdfd296529ca6549b4642440</t>
+          <t>0x6c8964e487e133d59a699205a9a6514d54217a61ad5ca3887aa005a89c8cbdfa</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6502,12 +6602,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -6534,7 +6634,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6564,7 +6664,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1784984405</t>
+          <t>1784984810</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6574,7 +6674,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>60.187328</t>
+          <t>58.209253</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6587,7 +6687,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xb07983b62c387b953f021bde51a561f510162701d56466ec78a20a598c01d8c4</t>
+          <t>0xb8b680dda4305fed43c95dc6dbc059c9678abe5f31da65b83ac57ecd5c8d3903</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6602,12 +6702,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -6634,7 +6734,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6664,7 +6764,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1784984404</t>
+          <t>1784984670</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6674,7 +6774,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>60.197529</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6687,27 +6787,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xc41db21ce0b5921299bba16424467dff9a9a6eb4d744a5aadf04422f8138f34f</t>
+          <t>0x374cde0708e064be0b99fea4bb71434540b7ca7bbd1a444cb12a8b14c6aa3c48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -6734,7 +6834,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6764,7 +6864,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1784984403</t>
+          <t>1784984617</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6774,7 +6874,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>29.185737</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6787,27 +6887,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x97d57842a441d56ad4d0172a6e2460bdd3644bd55476d419863d144ec4fb3f02</t>
+          <t>0x4c094ddc4f89a7cbd768baf6a26f7e686ead028a4b15ee75fd8f4927e1ad7989</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -6834,7 +6934,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6864,7 +6964,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1784984403</t>
+          <t>1784984581</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6874,7 +6974,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>4.444439</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6887,7 +6987,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x54a44d2ce4be4b546daee52057d4611c0f1d29571a9747f66b3462780e888ae0</t>
+          <t>0x7dd8d48e4f9e00707e79d58d5900292571189d9de19bd23c6c6a9a433ea96f72</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6902,12 +7002,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.2988</t>
+          <t>1.2712</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -6934,7 +7034,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6964,7 +7064,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1784984402</t>
+          <t>1784984563</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -6974,7 +7074,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>60.178243</t>
+          <t>60.198968</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -6987,7 +7087,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xf9d293335e6b1b3fd21eba9ec71cbbd6cbce398d5d606b38175d3776a077cb91</t>
+          <t>0x7354c940dd56ae7caca9fa9b1a548dcf53e1a3516f531216c677cf582affb4fe</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7002,12 +7102,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -7034,7 +7134,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xaf0827308b557ecc964e4c608c6b71f345660fa965da2a0e02882ee62ce45e49</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7064,7 +7164,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1784984401</t>
+          <t>1784984538</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7074,7 +7174,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>60.189781</t>
+          <t>31.184232</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7087,12 +7187,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x80f610f55e907d511b2c5a8d77d03f9aca143e4e50b6d7fba92997ba46481bde</t>
+          <t>0xdc3c1508859b265a9cc7ea3dadc58bb672f939bf46cde2c06081ec2891a03946</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7102,12 +7202,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -7134,7 +7234,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7164,7 +7264,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1784983849</t>
+          <t>1784984537</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7174,7 +7274,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>11.988786</t>
+          <t>48.297994</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7187,12 +7287,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x6e3d6f822ebfe70f563004b4a5a4a6303f1d1cb9677e6e3a56324cda8cc92ba7</t>
+          <t>0x0bf6c8f6ea5d7452bf543eb72d99a66c1b6ff74a5e56b4ad9449b6870f225d2d</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7202,12 +7302,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -7264,7 +7364,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1784983797</t>
+          <t>1784984536</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7274,7 +7374,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>46.150404</t>
+          <t>68.833427</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7287,27 +7387,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
+          <t>0xa4b5b4c3c3766e7d708b5373412745aa0b0d5f4c097f5451a2210d6d019269c6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -7334,7 +7434,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7364,7 +7464,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1784983703</t>
+          <t>1784984502</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7374,7 +7474,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>5.770489</t>
+          <t>53.355738</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7387,12 +7487,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
+          <t>0xfac3960037b540d1b0b49f14ff5313d7db5bd6320c356e510ef3e6bdaca6d1ff</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7402,12 +7502,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -7464,7 +7564,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1784983703</t>
+          <t>1784984501</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7474,7 +7574,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>4.389968</t>
+          <t>46.408957</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7487,12 +7587,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x589562dc55239bfc299045a0e5bbfed420cc8f286ee7326d34ed350f83ecdd45</t>
+          <t>0xf3b65016998beda20548812c7503abc20be0fa3abedc59c3ac7e08e6b82c70f1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7502,12 +7602,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -7534,7 +7634,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7564,7 +7664,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1784983480</t>
+          <t>1784984431</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7574,7 +7674,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>22.284118</t>
+          <t>22.912332</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7587,12 +7687,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x629a7bab69ed2f6eae5804065863061a8e5f95bfbf35104c3a1d130585e021ca</t>
+          <t>0xa04fcfb1b689fd17d1c3c66ac2ed73a6e0b99d30bdfd296529ca6549b4642440</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7602,12 +7702,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -7634,7 +7734,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7664,7 +7764,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1784983361</t>
+          <t>1784984405</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7674,7 +7774,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2.228408</t>
+          <t>60.187328</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7687,12 +7787,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x888b7311174b291a1eeccf40a054d1599070da16bd2f2f7adea95d18002cc686</t>
+          <t>0xb07983b62c387b953f021bde51a561f510162701d56466ec78a20a598c01d8c4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xB1854fc8aD8ce649EA80D007Fc67d318a239a5DA</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7702,12 +7802,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -7734,7 +7834,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7764,7 +7864,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1784981088</t>
+          <t>1784984404</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7774,7 +7874,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1.443442</t>
+          <t>60.197529</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7787,7 +7887,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x5d44678e836886d72dc3bddfca4b44d2be2bfa7f56096dbedd259cac92e30df3</t>
+          <t>0xc41db21ce0b5921299bba16424467dff9a9a6eb4d744a5aadf04422f8138f34f</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7802,7 +7902,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7864,7 +7964,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1784981082</t>
+          <t>1784984403</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -7874,7 +7974,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>21.377037</t>
+          <t>29.185737</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -7887,7 +7987,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x5a96bb0ca1d506186a0e2c1c2e13d657784bbb03ad3f75e66db86da80f485bae</t>
+          <t>0x97d57842a441d56ad4d0172a6e2460bdd3644bd55476d419863d144ec4fb3f02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7897,17 +7997,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -7934,7 +8034,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x2b00f05607bf61216841f59440e877cc0eeb424e834132492c721bd4faedc556</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7964,7 +8064,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1784980847</t>
+          <t>1784984403</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -7974,7 +8074,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>35.743728</t>
+          <t>4.444439</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -7987,12 +8087,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xe6e61e0b4573e8e2199880691f7803f1943269d2b2b955ea7282a833c4dbc3c6</t>
+          <t>0x54a44d2ce4be4b546daee52057d4611c0f1d29571a9747f66b3462780e888ae0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8002,12 +8102,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.2988</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -8034,7 +8134,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8064,7 +8164,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1784977858</t>
+          <t>1784984402</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8074,7 +8174,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>39.775279</t>
+          <t>60.178243</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8087,12 +8187,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x668fc309ba15ebe234fe9dd2d2bf696a9f4000c9ac85f8e7d55c998a052968dc</t>
+          <t>0xf9d293335e6b1b3fd21eba9ec71cbbd6cbce398d5d606b38175d3776a077cb91</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+          <t>0x4a09916b1325Eed50eE8973B13742a205B0B7c7E</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8102,12 +8202,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -8134,7 +8234,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+          <t>0xaf0827308b557ecc964e4c608c6b71f345660fa965da2a0e02882ee62ce45e49</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8164,7 +8264,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1784977853</t>
+          <t>1784984401</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8174,7 +8274,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>49.797748</t>
+          <t>60.189781</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8187,27 +8287,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xabcdef492212262464335967adbaa23c5214ede2fab0ea2a12bce6e0027067aa</t>
+          <t>0x80f610f55e907d511b2c5a8d77d03f9aca143e4e50b6d7fba92997ba46481bde</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -8234,7 +8334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8264,7 +8364,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1784968614</t>
+          <t>1784983849</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8274,7 +8374,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>47.149425</t>
+          <t>11.988786</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8287,12 +8387,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xf7e34584abe1fc7da16770ad9dc2fe59e91a45480c1ff509d55070c7d811c7e2</t>
+          <t>0x6e3d6f822ebfe70f563004b4a5a4a6303f1d1cb9677e6e3a56324cda8cc92ba7</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x516bfc7CE57c0E1734388ECed5Bb9454aA6aeFae</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8302,12 +8402,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -8334,7 +8434,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8364,7 +8464,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1784907257</t>
+          <t>1784983797</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8374,7 +8474,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>17.857143</t>
+          <t>46.150404</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8387,27 +8487,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x030841d8eff7e23d98d8319e71f99f9eb17cb2a743343cfac134410b86f1178e</t>
+          <t>0xc913b7104d801ceb0283dc9eefcce577969c93f7b16c1cc5515036561b5b8d8e</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.7712</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -8434,7 +8534,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8464,7 +8564,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1784907053</t>
+          <t>1784983703</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8474,7 +8574,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>46.28739</t>
+          <t>5.770489</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8487,12 +8587,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xd486facb98ea7c7e7b67efb74b5231332788279dbd71dce40eea54aecf5d870e</t>
+          <t>0x78c593e23cd10a2517f77039f922e2d360ba0b6d4c89dc91bac22f6854ce01ea</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8502,12 +8602,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -8534,7 +8634,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8564,7 +8664,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1784907041</t>
+          <t>1784983703</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8574,7 +8674,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>47.587302</t>
+          <t>4.389968</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8587,12 +8687,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x8a9596cb004924470885fe466db8f8d059fcb9d1b24e71490dd35bfeba65a98d</t>
+          <t>0x589562dc55239bfc299045a0e5bbfed420cc8f286ee7326d34ed350f83ecdd45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8602,12 +8702,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -8634,7 +8734,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8664,7 +8764,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1784907041</t>
+          <t>1784983480</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8674,7 +8774,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>47.555556</t>
+          <t>22.284118</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8687,12 +8787,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+          <t>0x629a7bab69ed2f6eae5804065863061a8e5f95bfbf35104c3a1d130585e021ca</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8702,12 +8802,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -8734,7 +8834,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8764,7 +8864,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1784907040</t>
+          <t>1784983361</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -8774,7 +8874,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>47.046509</t>
+          <t>2.228408</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -8787,12 +8887,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+          <t>0x888b7311174b291a1eeccf40a054d1599070da16bd2f2f7adea95d18002cc686</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+          <t>0xB1854fc8aD8ce649EA80D007Fc67d318a239a5DA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8802,12 +8902,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -8834,55 +8934,1155 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1784981088</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1.443442</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0x5d44678e836886d72dc3bddfca4b44d2be2bfa7f56096dbedd259cac92e30df3</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.7712</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0x91a9ea8ebfd8b049218a8e072590d2f657e26fdb1f2a49b1016ae42171c68ef2</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1784981082</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>21.377037</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0x5a96bb0ca1d506186a0e2c1c2e13d657784bbb03ad3f75e66db86da80f485bae</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1784980847</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>35.743728</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0xe6e61e0b4573e8e2199880691f7803f1943269d2b2b955ea7282a833c4dbc3c6</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1784977858</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>39.775279</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0x668fc309ba15ebe234fe9dd2d2bf696a9f4000c9ac85f8e7d55c998a052968dc</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0x47D0CE9b8d653c8884DB7E2a7F88d4849E0CD980</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0x04fd78e33c10fb928e409323c26948f49fe4c81fcd47748d9153c9c611b38d0b</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1784977853</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>49.797748</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0xabcdef492212262464335967adbaa23c5214ede2fab0ea2a12bce6e0027067aa</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.435</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0xef2cff3047642c7d3f79713526decc2ed1438c01d374590eb62929362f824801</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1784968614</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>47.149425</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0xf7e34584abe1fc7da16770ad9dc2fe59e91a45480c1ff509d55070c7d811c7e2</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0x516bfc7CE57c0E1734388ECed5Bb9454aA6aeFae</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1784907257</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>17.857143</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0x030841d8eff7e23d98d8319e71f99f9eb17cb2a743343cfac134410b86f1178e</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.5737</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1784907053</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>46.28739</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0xd486facb98ea7c7e7b67efb74b5231332788279dbd71dce40eea54aecf5d870e</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0x588a71865f90131e16b5b72dfef6ddb7cec8deb7df1f8102477a62eaa807cc71</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>47.587302</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0x8a9596cb004924470885fe466db8f8d059fcb9d1b24e71490dd35bfeba65a98d</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0x06a233f1b733d63cee459a37ac1beffad92b8f9ec21c414e0c26e2876b05eebd</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1784907041</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>47.555556</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0xdaf8fe8a287cecb340987a0eebd287e9d8e007af24d015fcadd720fceba485cd</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0xe1204c11efd43d8d3a0377591c468bba3ac169f58ab541c6d60665f2e0bbb051</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19520873</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1784907040</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1784988000</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>47.046509</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0x3f981c0415a637d3cb9137ae5b4b0b4b0c50f1a3af5d4e42f65e682f80daadba</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0xC88F614A48f8A705d7465b03aAF62ddaca0c3754</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Besta Deild Karla</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>IR Reykjavik vs Fylkir</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
           <t>0xd5ae8f2322bcc6adaca1c1bb1baf6a74afa50cc30131840c87632f67865c23d0</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>L19520873</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
         <is>
           <t>1784907040</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>1784988000</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>47.589189</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
